--- a/research/traditional_assets/database/data/croatia/croatia_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_beverage_alcoholic.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08678657186807702</v>
+        <v>0.08666725603871447</v>
       </c>
       <c r="C2">
-        <v>55.4319717831</v>
+        <v>54.96926390982862</v>
       </c>
       <c r="D2">
-        <v>51.0419717831</v>
+        <v>51.12426390982862</v>
       </c>
       <c r="E2">
-        <v>-19</v>
+        <v>-18.455</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="G2">
         <v>4.39</v>
@@ -1451,28 +1451,28 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0274135</v>
       </c>
       <c r="N2">
-        <v>2.01530612244898</v>
+        <v>1.98789262244898</v>
       </c>
       <c r="O2">
-        <v>0.3627551020408163</v>
+        <v>0.3578206720408164</v>
       </c>
       <c r="P2">
-        <v>1.652551020408163</v>
+        <v>1.630071950408163</v>
       </c>
       <c r="Q2">
-        <v>4.902551020408163</v>
+        <v>4.880071950408164</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08678657186807702</v>
+        <v>0.08712605660476209</v>
       </c>
       <c r="T2">
-        <v>0.6910924838905985</v>
+        <v>0.6968166842622175</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>73.51509739540663</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08666725603871447</v>
+        <v>0.08654794020935194</v>
       </c>
       <c r="C3">
-        <v>54.96926390982862</v>
+        <v>54.5068218150773</v>
       </c>
       <c r="D3">
-        <v>51.12426390982862</v>
+        <v>51.2068218150773</v>
       </c>
       <c r="E3">
-        <v>-18.455</v>
+        <v>-17.91</v>
       </c>
       <c r="F3">
-        <v>0.545</v>
+        <v>1.09</v>
       </c>
       <c r="G3">
         <v>4.39</v>
@@ -1533,28 +1533,28 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M3">
-        <v>0.0274135</v>
+        <v>0.054827</v>
       </c>
       <c r="N3">
-        <v>1.98789262244898</v>
+        <v>1.96047912244898</v>
       </c>
       <c r="O3">
-        <v>0.3578206720408164</v>
+        <v>0.3528862420408163</v>
       </c>
       <c r="P3">
-        <v>1.630071950408163</v>
+        <v>1.607592880408163</v>
       </c>
       <c r="Q3">
-        <v>4.880071950408164</v>
+        <v>4.857592880408164</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08712605660476209</v>
+        <v>0.08747246960137953</v>
       </c>
       <c r="T3">
-        <v>0.6968166842622175</v>
+        <v>0.702657705049584</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>73.51509739540663</v>
+        <v>36.75754869770331</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08654794020935194</v>
+        <v>0.0864286243799894</v>
       </c>
       <c r="C4">
-        <v>54.5068218150773</v>
+        <v>54.04464678850427</v>
       </c>
       <c r="D4">
-        <v>51.2068218150773</v>
+        <v>51.28964678850427</v>
       </c>
       <c r="E4">
-        <v>-17.91</v>
+        <v>-17.365</v>
       </c>
       <c r="F4">
-        <v>1.09</v>
+        <v>1.635</v>
       </c>
       <c r="G4">
         <v>4.39</v>
@@ -1615,28 +1615,28 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M4">
-        <v>0.054827</v>
+        <v>0.08224049999999999</v>
       </c>
       <c r="N4">
-        <v>1.96047912244898</v>
+        <v>1.93306562244898</v>
       </c>
       <c r="O4">
-        <v>0.3528862420408163</v>
+        <v>0.3479518120408163</v>
       </c>
       <c r="P4">
-        <v>1.607592880408163</v>
+        <v>1.585113810408163</v>
       </c>
       <c r="Q4">
-        <v>4.857592880408164</v>
+        <v>4.835113810408163</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08747246960137953</v>
+        <v>0.08782602513400969</v>
       </c>
       <c r="T4">
-        <v>0.702657705049584</v>
+        <v>0.7086191592552468</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>36.75754869770331</v>
+        <v>24.50503246513555</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0864286243799894</v>
+        <v>0.08630930855062685</v>
       </c>
       <c r="C5">
-        <v>54.04464678850427</v>
+        <v>53.58274012812509</v>
       </c>
       <c r="D5">
-        <v>51.28964678850427</v>
+        <v>51.37274012812509</v>
       </c>
       <c r="E5">
-        <v>-17.365</v>
+        <v>-16.82</v>
       </c>
       <c r="F5">
-        <v>1.635</v>
+        <v>2.18</v>
       </c>
       <c r="G5">
         <v>4.39</v>
@@ -1697,28 +1697,28 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M5">
-        <v>0.08224049999999999</v>
+        <v>0.109654</v>
       </c>
       <c r="N5">
-        <v>1.93306562244898</v>
+        <v>1.90565212244898</v>
       </c>
       <c r="O5">
-        <v>0.3479518120408163</v>
+        <v>0.3430173820408163</v>
       </c>
       <c r="P5">
-        <v>1.585113810408163</v>
+        <v>1.562634740408163</v>
       </c>
       <c r="Q5">
-        <v>4.835113810408163</v>
+        <v>4.812634740408163</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08782602513400969</v>
+        <v>0.08818694640690297</v>
       </c>
       <c r="T5">
-        <v>0.7086191592552468</v>
+        <v>0.7147048104235273</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>24.50503246513555</v>
+        <v>18.37877434885166</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08630930855062685</v>
+        <v>0.08618999272126432</v>
       </c>
       <c r="C6">
-        <v>53.58274012812509</v>
+        <v>53.1211031403805</v>
       </c>
       <c r="D6">
-        <v>51.37274012812509</v>
+        <v>51.4561031403805</v>
       </c>
       <c r="E6">
-        <v>-16.82</v>
+        <v>-16.275</v>
       </c>
       <c r="F6">
-        <v>2.18</v>
+        <v>2.725</v>
       </c>
       <c r="G6">
         <v>4.39</v>
@@ -1779,28 +1779,28 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M6">
-        <v>0.109654</v>
+        <v>0.1370675</v>
       </c>
       <c r="N6">
-        <v>1.90565212244898</v>
+        <v>1.87823862244898</v>
       </c>
       <c r="O6">
-        <v>0.3430173820408163</v>
+        <v>0.3380829520408163</v>
       </c>
       <c r="P6">
-        <v>1.562634740408163</v>
+        <v>1.540155670408163</v>
       </c>
       <c r="Q6">
-        <v>4.812634740408163</v>
+        <v>4.790155670408163</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08818694640690297</v>
+        <v>0.0885554660223835</v>
       </c>
       <c r="T6">
-        <v>0.7147048104235273</v>
+        <v>0.7209185805637717</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>18.37877434885166</v>
+        <v>14.70301947908133</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08618999272126432</v>
+        <v>0.08614447689190177</v>
       </c>
       <c r="C7">
-        <v>53.1211031403805</v>
+        <v>52.60797525497541</v>
       </c>
       <c r="D7">
-        <v>51.4561031403805</v>
+        <v>51.48797525497542</v>
       </c>
       <c r="E7">
-        <v>-16.275</v>
+        <v>-15.73</v>
       </c>
       <c r="F7">
-        <v>2.725</v>
+        <v>3.27</v>
       </c>
       <c r="G7">
         <v>4.39</v>
@@ -1861,45 +1861,45 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M7">
-        <v>0.1370675</v>
+        <v>0.169386</v>
       </c>
       <c r="N7">
-        <v>1.87823862244898</v>
+        <v>1.84592012244898</v>
       </c>
       <c r="O7">
-        <v>0.3380829520408163</v>
+        <v>0.3322656220408163</v>
       </c>
       <c r="P7">
-        <v>1.540155670408163</v>
+        <v>1.513654500408163</v>
       </c>
       <c r="Q7">
-        <v>4.790155670408163</v>
+        <v>4.763654500408164</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0885554660223835</v>
+        <v>0.08893182648074657</v>
       </c>
       <c r="T7">
-        <v>0.7209185805637717</v>
+        <v>0.7272645585793405</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.18</v>
       </c>
       <c r="W7">
-        <v>0.041246</v>
+        <v>0.042476</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>14.70301947908133</v>
+        <v>11.8977136389606</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08614447689190177</v>
+        <v>0.08603746106253926</v>
       </c>
       <c r="C8">
-        <v>52.60797525497541</v>
+        <v>52.13806805465096</v>
       </c>
       <c r="D8">
-        <v>51.48797525497542</v>
+        <v>51.56306805465096</v>
       </c>
       <c r="E8">
-        <v>-15.73</v>
+        <v>-15.185</v>
       </c>
       <c r="F8">
-        <v>3.27</v>
+        <v>3.815</v>
       </c>
       <c r="G8">
         <v>4.39</v>
@@ -1943,28 +1943,28 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M8">
-        <v>0.169386</v>
+        <v>0.197617</v>
       </c>
       <c r="N8">
-        <v>1.84592012244898</v>
+        <v>1.81768912244898</v>
       </c>
       <c r="O8">
-        <v>0.3322656220408163</v>
+        <v>0.3271840420408164</v>
       </c>
       <c r="P8">
-        <v>1.513654500408163</v>
+        <v>1.490505080408163</v>
       </c>
       <c r="Q8">
-        <v>4.763654500408164</v>
+        <v>4.740505080408163</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08893182648074657</v>
+        <v>0.0893162807124078</v>
       </c>
       <c r="T8">
-        <v>0.7272645585793405</v>
+        <v>0.7337470092404054</v>
       </c>
       <c r="U8">
         <v>0.0518</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>11.8977136389606</v>
+        <v>10.19804026196623</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08603746106253925</v>
+        <v>0.08604196523317671</v>
       </c>
       <c r="C9">
-        <v>52.13806805465097</v>
+        <v>51.58990307160133</v>
       </c>
       <c r="D9">
-        <v>51.56306805465096</v>
+        <v>51.55990307160133</v>
       </c>
       <c r="E9">
-        <v>-15.185</v>
+        <v>-14.64</v>
       </c>
       <c r="F9">
-        <v>3.815</v>
+        <v>4.36</v>
       </c>
       <c r="G9">
         <v>4.39</v>
@@ -2025,45 +2025,45 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M9">
-        <v>0.197617</v>
+        <v>0.23326</v>
       </c>
       <c r="N9">
-        <v>1.81768912244898</v>
+        <v>1.78204612244898</v>
       </c>
       <c r="O9">
-        <v>0.3271840420408164</v>
+        <v>0.3207683020408163</v>
       </c>
       <c r="P9">
-        <v>1.490505080408163</v>
+        <v>1.461277820408163</v>
       </c>
       <c r="Q9">
-        <v>4.740505080408163</v>
+        <v>4.711277820408164</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0893162807124078</v>
+        <v>0.08970909264475729</v>
       </c>
       <c r="T9">
-        <v>0.7337470092404054</v>
+        <v>0.7403703827419282</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0.18</v>
       </c>
       <c r="W9">
-        <v>0.042476</v>
+        <v>0.04387</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>10.19804026196623</v>
+        <v>8.639741586422787</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08604196523317671</v>
+        <v>0.08594888940381418</v>
       </c>
       <c r="C10">
-        <v>51.58990307160133</v>
+        <v>51.11038448074709</v>
       </c>
       <c r="D10">
-        <v>51.55990307160133</v>
+        <v>51.62538448074709</v>
       </c>
       <c r="E10">
-        <v>-14.64</v>
+        <v>-14.095</v>
       </c>
       <c r="F10">
-        <v>4.36</v>
+        <v>4.905</v>
       </c>
       <c r="G10">
         <v>4.39</v>
@@ -2107,28 +2107,28 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M10">
-        <v>0.23326</v>
+        <v>0.2624175</v>
       </c>
       <c r="N10">
-        <v>1.78204612244898</v>
+        <v>1.75288862244898</v>
       </c>
       <c r="O10">
-        <v>0.3207683020408163</v>
+        <v>0.3155199520408163</v>
       </c>
       <c r="P10">
-        <v>1.461277820408163</v>
+        <v>1.437368670408163</v>
       </c>
       <c r="Q10">
-        <v>4.711277820408164</v>
+        <v>4.687368670408164</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08970909264475729</v>
+        <v>0.0901105378063892</v>
       </c>
       <c r="T10">
-        <v>0.7403703827419282</v>
+        <v>0.7471393248918361</v>
       </c>
       <c r="U10">
         <v>0.0535</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>8.639741586422787</v>
+        <v>7.679770299042478</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08594888940381418</v>
+        <v>0.08592141357445163</v>
       </c>
       <c r="C11">
-        <v>51.11038448074709</v>
+        <v>50.58474629139671</v>
       </c>
       <c r="D11">
-        <v>51.62538448074709</v>
+        <v>51.64474629139671</v>
       </c>
       <c r="E11">
-        <v>-14.095</v>
+        <v>-13.55</v>
       </c>
       <c r="F11">
-        <v>4.905</v>
+        <v>5.449999999999999</v>
       </c>
       <c r="G11">
         <v>4.39</v>
@@ -2189,45 +2189,45 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M11">
-        <v>0.2624175</v>
+        <v>0.2959349999999999</v>
       </c>
       <c r="N11">
-        <v>1.75288862244898</v>
+        <v>1.71937112244898</v>
       </c>
       <c r="O11">
-        <v>0.3155199520408163</v>
+        <v>0.3094868020408163</v>
       </c>
       <c r="P11">
-        <v>1.437368670408163</v>
+        <v>1.409884320408163</v>
       </c>
       <c r="Q11">
-        <v>4.687368670408164</v>
+        <v>4.659884320408163</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0901105378063892</v>
+        <v>0.09052090397161291</v>
       </c>
       <c r="T11">
-        <v>0.7471393248918361</v>
+        <v>0.7540586879784086</v>
       </c>
       <c r="U11">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V11">
         <v>0.18</v>
       </c>
       <c r="W11">
-        <v>0.04387</v>
+        <v>0.044526</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y11">
-        <v>7.679770299042478</v>
+        <v>6.809962060753138</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08592141357445163</v>
+        <v>0.08583489774508909</v>
       </c>
       <c r="C12">
-        <v>50.58474629139671</v>
+        <v>50.10080769188492</v>
       </c>
       <c r="D12">
-        <v>51.64474629139671</v>
+        <v>51.70580769188492</v>
       </c>
       <c r="E12">
-        <v>-13.55</v>
+        <v>-13.005</v>
       </c>
       <c r="F12">
-        <v>5.45</v>
+        <v>5.995</v>
       </c>
       <c r="G12">
         <v>4.39</v>
@@ -2271,28 +2271,28 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M12">
-        <v>0.295935</v>
+        <v>0.3255285</v>
       </c>
       <c r="N12">
-        <v>1.71937112244898</v>
+        <v>1.68977762244898</v>
       </c>
       <c r="O12">
-        <v>0.3094868020408163</v>
+        <v>0.3041599720408164</v>
       </c>
       <c r="P12">
-        <v>1.409884320408163</v>
+        <v>1.385617650408163</v>
       </c>
       <c r="Q12">
-        <v>4.659884320408163</v>
+        <v>4.635617650408164</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09052090397161291</v>
+        <v>0.09094049184841471</v>
       </c>
       <c r="T12">
-        <v>0.7540586879784086</v>
+        <v>0.7611335423702974</v>
       </c>
       <c r="U12">
         <v>0.0543</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>6.809962060753137</v>
+        <v>6.190874600684671</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08583489774508909</v>
+        <v>0.08584678191572656</v>
       </c>
       <c r="C13">
-        <v>50.10080769188492</v>
+        <v>49.54741149305389</v>
       </c>
       <c r="D13">
-        <v>51.70580769188492</v>
+        <v>51.69741149305388</v>
       </c>
       <c r="E13">
-        <v>-13.005</v>
+        <v>-12.46</v>
       </c>
       <c r="F13">
-        <v>5.995</v>
+        <v>6.54</v>
       </c>
       <c r="G13">
         <v>4.39</v>
@@ -2353,45 +2353,45 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M13">
-        <v>0.3255285</v>
+        <v>0.361662</v>
       </c>
       <c r="N13">
-        <v>1.68977762244898</v>
+        <v>1.65364412244898</v>
       </c>
       <c r="O13">
-        <v>0.3041599720408164</v>
+        <v>0.2976559420408164</v>
       </c>
       <c r="P13">
-        <v>1.385617650408163</v>
+        <v>1.355988180408163</v>
       </c>
       <c r="Q13">
-        <v>4.635617650408164</v>
+        <v>4.605988180408163</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09094049184841471</v>
+        <v>0.09136961581332563</v>
       </c>
       <c r="T13">
-        <v>0.7611335423702974</v>
+        <v>0.7683691889074563</v>
       </c>
       <c r="U13">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V13">
         <v>0.18</v>
       </c>
       <c r="W13">
-        <v>0.044526</v>
+        <v>0.045346</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y13">
-        <v>6.190874600684671</v>
+        <v>5.572346894196735</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08584678191572656</v>
+        <v>0.08576846608636401</v>
       </c>
       <c r="C14">
-        <v>49.54741149305389</v>
+        <v>49.05779211719124</v>
       </c>
       <c r="D14">
-        <v>51.69741149305388</v>
+        <v>51.75279211719124</v>
       </c>
       <c r="E14">
-        <v>-12.46</v>
+        <v>-11.915</v>
       </c>
       <c r="F14">
-        <v>6.54</v>
+        <v>7.085</v>
       </c>
       <c r="G14">
         <v>4.39</v>
@@ -2435,28 +2435,28 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M14">
-        <v>0.361662</v>
+        <v>0.3918005</v>
       </c>
       <c r="N14">
-        <v>1.65364412244898</v>
+        <v>1.62350562244898</v>
       </c>
       <c r="O14">
-        <v>0.2976559420408164</v>
+        <v>0.2922310120408163</v>
       </c>
       <c r="P14">
-        <v>1.355988180408163</v>
+        <v>1.331274610408163</v>
       </c>
       <c r="Q14">
-        <v>4.605988180408163</v>
+        <v>4.581274610408164</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09136961581332563</v>
+        <v>0.09180860469697014</v>
       </c>
       <c r="T14">
-        <v>0.7683691889074563</v>
+        <v>0.7757711721466191</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.572346894196735</v>
+        <v>5.143704825412371</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08576846608636401</v>
+        <v>0.08569015025700147</v>
       </c>
       <c r="C15">
-        <v>49.05779211719124</v>
+        <v>48.56829152106977</v>
       </c>
       <c r="D15">
-        <v>51.75279211719124</v>
+        <v>51.80829152106978</v>
       </c>
       <c r="E15">
-        <v>-11.915</v>
+        <v>-11.37</v>
       </c>
       <c r="F15">
-        <v>7.085</v>
+        <v>7.630000000000001</v>
       </c>
       <c r="G15">
         <v>4.39</v>
@@ -2517,28 +2517,28 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M15">
-        <v>0.3918005</v>
+        <v>0.4219390000000001</v>
       </c>
       <c r="N15">
-        <v>1.62350562244898</v>
+        <v>1.59336712244898</v>
       </c>
       <c r="O15">
-        <v>0.2922310120408163</v>
+        <v>0.2868060820408163</v>
       </c>
       <c r="P15">
-        <v>1.331274610408163</v>
+        <v>1.306561040408163</v>
       </c>
       <c r="Q15">
-        <v>4.581274610408164</v>
+        <v>4.556561040408163</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09180860469697014</v>
+        <v>0.09225780262442032</v>
       </c>
       <c r="T15">
-        <v>0.7757711721466191</v>
+        <v>0.7833452945308784</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.143704825412371</v>
+        <v>4.776297337882915</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08569015025700147</v>
+        <v>0.08591933442763894</v>
       </c>
       <c r="C16">
-        <v>48.56829152106977</v>
+        <v>47.86121202650202</v>
       </c>
       <c r="D16">
-        <v>51.80829152106978</v>
+        <v>51.64621202650202</v>
       </c>
       <c r="E16">
-        <v>-11.37</v>
+        <v>-10.825</v>
       </c>
       <c r="F16">
-        <v>7.630000000000001</v>
+        <v>8.175000000000001</v>
       </c>
       <c r="G16">
         <v>4.39</v>
@@ -2599,45 +2599,45 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M16">
-        <v>0.4219390000000001</v>
+        <v>0.4725150000000001</v>
       </c>
       <c r="N16">
-        <v>1.59336712244898</v>
+        <v>1.54279112244898</v>
       </c>
       <c r="O16">
-        <v>0.2868060820408163</v>
+        <v>0.2777024020408163</v>
       </c>
       <c r="P16">
-        <v>1.306561040408163</v>
+        <v>1.265088720408163</v>
       </c>
       <c r="Q16">
-        <v>4.556561040408163</v>
+        <v>4.515088720408164</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09225780262442032</v>
+        <v>0.09271756991486935</v>
       </c>
       <c r="T16">
-        <v>0.7833452945308784</v>
+        <v>0.7910976315594734</v>
       </c>
       <c r="U16">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V16">
         <v>0.18</v>
       </c>
       <c r="W16">
-        <v>0.045346</v>
+        <v>0.04739600000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.776297337882915</v>
+        <v>4.265062743931895</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08591933442763894</v>
+        <v>0.08632071859827641</v>
       </c>
       <c r="C17">
-        <v>47.86121202650202</v>
+        <v>47.03478235869129</v>
       </c>
       <c r="D17">
-        <v>51.64621202650202</v>
+        <v>51.36478235869129</v>
       </c>
       <c r="E17">
-        <v>-10.825</v>
+        <v>-10.28</v>
       </c>
       <c r="F17">
-        <v>8.174999999999999</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G17">
         <v>4.39</v>
@@ -2681,45 +2681,45 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M17">
-        <v>0.472515</v>
+        <v>0.534536</v>
       </c>
       <c r="N17">
-        <v>1.54279112244898</v>
+        <v>1.48077012244898</v>
       </c>
       <c r="O17">
-        <v>0.2777024020408163</v>
+        <v>0.2665386220408163</v>
       </c>
       <c r="P17">
-        <v>1.265088720408163</v>
+        <v>1.214231500408163</v>
       </c>
       <c r="Q17">
-        <v>4.515088720408164</v>
+        <v>4.464231500408163</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09271756991486935</v>
+        <v>0.09318828404556714</v>
       </c>
       <c r="T17">
-        <v>0.7910976315594734</v>
+        <v>0.7990345480411302</v>
       </c>
       <c r="U17">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V17">
         <v>0.18</v>
       </c>
       <c r="W17">
-        <v>0.04739600000000001</v>
+        <v>0.05026600000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.265062743931896</v>
+        <v>3.770197184939797</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08632071859827641</v>
+        <v>0.08629160276891387</v>
       </c>
       <c r="C18">
-        <v>47.03478235869129</v>
+        <v>46.51009364746707</v>
       </c>
       <c r="D18">
-        <v>51.36478235869129</v>
+        <v>51.38509364746707</v>
       </c>
       <c r="E18">
-        <v>-10.28</v>
+        <v>-9.734999999999999</v>
       </c>
       <c r="F18">
-        <v>8.720000000000001</v>
+        <v>9.265000000000001</v>
       </c>
       <c r="G18">
         <v>4.39</v>
@@ -2763,28 +2763,28 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M18">
-        <v>0.534536</v>
+        <v>0.5679445000000001</v>
       </c>
       <c r="N18">
-        <v>1.48077012244898</v>
+        <v>1.44736162244898</v>
       </c>
       <c r="O18">
-        <v>0.2665386220408163</v>
+        <v>0.2605250920408163</v>
       </c>
       <c r="P18">
-        <v>1.214231500408163</v>
+        <v>1.186836530408163</v>
       </c>
       <c r="Q18">
-        <v>4.464231500408163</v>
+        <v>4.436836530408163</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09318828404556714</v>
+        <v>0.09367034068543839</v>
       </c>
       <c r="T18">
-        <v>0.7990345480411302</v>
+        <v>0.8071627155223449</v>
       </c>
       <c r="U18">
         <v>0.0613</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.770197184939797</v>
+        <v>3.548420879943338</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08629160276891387</v>
+        <v>0.08667576693955131</v>
       </c>
       <c r="C19">
-        <v>46.51009364746707</v>
+        <v>45.69838515382781</v>
       </c>
       <c r="D19">
-        <v>51.38509364746707</v>
+        <v>51.11838515382782</v>
       </c>
       <c r="E19">
-        <v>-9.734999999999999</v>
+        <v>-9.19</v>
       </c>
       <c r="F19">
-        <v>9.265000000000001</v>
+        <v>9.81</v>
       </c>
       <c r="G19">
         <v>4.39</v>
@@ -2845,45 +2845,45 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M19">
-        <v>0.5679445000000001</v>
+        <v>0.6288210000000001</v>
       </c>
       <c r="N19">
-        <v>1.44736162244898</v>
+        <v>1.38648512244898</v>
       </c>
       <c r="O19">
-        <v>0.2605250920408163</v>
+        <v>0.2495673220408163</v>
       </c>
       <c r="P19">
-        <v>1.186836530408163</v>
+        <v>1.136917800408163</v>
       </c>
       <c r="Q19">
-        <v>4.436836530408163</v>
+        <v>4.386917800408163</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09367034068543839</v>
+        <v>0.09416415480433088</v>
       </c>
       <c r="T19">
-        <v>0.8071627155223449</v>
+        <v>0.8154891309909064</v>
       </c>
       <c r="U19">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V19">
         <v>0.18</v>
       </c>
       <c r="W19">
-        <v>0.05026600000000001</v>
+        <v>0.052562</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>3.548420879943338</v>
+        <v>3.204896341644092</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08667576693955133</v>
+        <v>0.08666961111018878</v>
       </c>
       <c r="C20">
-        <v>45.69838515382781</v>
+        <v>45.15763705006256</v>
       </c>
       <c r="D20">
-        <v>51.11838515382782</v>
+        <v>51.12263705006256</v>
       </c>
       <c r="E20">
-        <v>-9.19</v>
+        <v>-8.645</v>
       </c>
       <c r="F20">
-        <v>9.81</v>
+        <v>10.355</v>
       </c>
       <c r="G20">
         <v>4.39</v>
@@ -2927,28 +2927,28 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M20">
-        <v>0.6288210000000001</v>
+        <v>0.6637555000000001</v>
       </c>
       <c r="N20">
-        <v>1.38648512244898</v>
+        <v>1.351550622448979</v>
       </c>
       <c r="O20">
-        <v>0.2495673220408163</v>
+        <v>0.2432791120408163</v>
       </c>
       <c r="P20">
-        <v>1.136917800408163</v>
+        <v>1.108271510408163</v>
       </c>
       <c r="Q20">
-        <v>4.386917800408163</v>
+        <v>4.358271510408163</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09416415480433088</v>
+        <v>0.09467016186443059</v>
       </c>
       <c r="T20">
-        <v>0.8154891309909063</v>
+        <v>0.8240211369648642</v>
       </c>
       <c r="U20">
         <v>0.0641</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.204896341644092</v>
+        <v>3.036217586820718</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08666961111018878</v>
+        <v>0.08794265528082625</v>
       </c>
       <c r="C21">
-        <v>45.15763705006256</v>
+        <v>43.74812957496285</v>
       </c>
       <c r="D21">
-        <v>51.12263705006256</v>
+        <v>50.25812957496284</v>
       </c>
       <c r="E21">
-        <v>-8.645</v>
+        <v>-8.1</v>
       </c>
       <c r="F21">
-        <v>10.355</v>
+        <v>10.9</v>
       </c>
       <c r="G21">
         <v>4.39</v>
@@ -3009,45 +3009,45 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M21">
-        <v>0.6637555000000001</v>
+        <v>0.7837100000000001</v>
       </c>
       <c r="N21">
-        <v>1.351550622448979</v>
+        <v>1.23159612244898</v>
       </c>
       <c r="O21">
-        <v>0.2432791120408163</v>
+        <v>0.2216873020408163</v>
       </c>
       <c r="P21">
-        <v>1.108271510408163</v>
+        <v>1.009908820408163</v>
       </c>
       <c r="Q21">
-        <v>4.358271510408163</v>
+        <v>4.259908820408163</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09467016186443059</v>
+        <v>0.0951888191010328</v>
       </c>
       <c r="T21">
-        <v>0.8240211369648642</v>
+        <v>0.8327664430881713</v>
       </c>
       <c r="U21">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V21">
         <v>0.18</v>
       </c>
       <c r="W21">
-        <v>0.052562</v>
+        <v>0.05895800000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.036217586820718</v>
+        <v>2.571494714178688</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08794265528082625</v>
+        <v>0.08867203945146371</v>
       </c>
       <c r="C22">
-        <v>43.74812957496285</v>
+        <v>42.72086299790877</v>
       </c>
       <c r="D22">
-        <v>50.25812957496284</v>
+        <v>49.77586299790877</v>
       </c>
       <c r="E22">
-        <v>-8.1</v>
+        <v>-7.555</v>
       </c>
       <c r="F22">
-        <v>10.9</v>
+        <v>11.445</v>
       </c>
       <c r="G22">
         <v>4.39</v>
@@ -3091,45 +3091,45 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M22">
-        <v>0.7837100000000001</v>
+        <v>0.8675310000000001</v>
       </c>
       <c r="N22">
-        <v>1.23159612244898</v>
+        <v>1.14777512244898</v>
       </c>
       <c r="O22">
-        <v>0.2216873020408163</v>
+        <v>0.2065995220408163</v>
       </c>
       <c r="P22">
-        <v>1.009908820408163</v>
+        <v>0.9411756004081633</v>
       </c>
       <c r="Q22">
-        <v>4.259908820408163</v>
+        <v>4.191175600408164</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0951888191010328</v>
+        <v>0.09572060690058697</v>
       </c>
       <c r="T22">
-        <v>0.8327664430881713</v>
+        <v>0.8417331493664986</v>
       </c>
       <c r="U22">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V22">
         <v>0.18</v>
       </c>
       <c r="W22">
-        <v>0.05895800000000001</v>
+        <v>0.06215600000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y22">
-        <v>2.571494714178688</v>
+        <v>2.323036436103124</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08867203945146371</v>
+        <v>0.08876182362210118</v>
       </c>
       <c r="C23">
-        <v>42.72086299790877</v>
+        <v>42.11713700126899</v>
       </c>
       <c r="D23">
-        <v>49.77586299790877</v>
+        <v>49.71713700126899</v>
       </c>
       <c r="E23">
-        <v>-7.555</v>
+        <v>-7.01</v>
       </c>
       <c r="F23">
-        <v>11.445</v>
+        <v>11.99</v>
       </c>
       <c r="G23">
         <v>4.39</v>
@@ -3173,28 +3173,28 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M23">
-        <v>0.8675310000000001</v>
+        <v>0.908842</v>
       </c>
       <c r="N23">
-        <v>1.14777512244898</v>
+        <v>1.10646412244898</v>
       </c>
       <c r="O23">
-        <v>0.2065995220408163</v>
+        <v>0.1991635420408163</v>
       </c>
       <c r="P23">
-        <v>0.9411756004081633</v>
+        <v>0.9073005804081634</v>
       </c>
       <c r="Q23">
-        <v>4.191175600408164</v>
+        <v>4.157300580408164</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09572060690058697</v>
+        <v>0.09626603028474509</v>
       </c>
       <c r="T23">
-        <v>0.8417331493664986</v>
+        <v>0.8509297711904241</v>
       </c>
       <c r="U23">
         <v>0.07580000000000001</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.323036436103124</v>
+        <v>2.21744387082571</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08876182362210118</v>
+        <v>0.08885160779273862</v>
       </c>
       <c r="C24">
-        <v>42.11713700126899</v>
+        <v>41.51354941221925</v>
       </c>
       <c r="D24">
-        <v>49.71713700126899</v>
+        <v>49.65854941221924</v>
       </c>
       <c r="E24">
-        <v>-7.01</v>
+        <v>-6.465</v>
       </c>
       <c r="F24">
-        <v>11.99</v>
+        <v>12.535</v>
       </c>
       <c r="G24">
         <v>4.39</v>
@@ -3255,28 +3255,28 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M24">
-        <v>0.908842</v>
+        <v>0.9501530000000001</v>
       </c>
       <c r="N24">
-        <v>1.10646412244898</v>
+        <v>1.065153122448979</v>
       </c>
       <c r="O24">
-        <v>0.1991635420408163</v>
+        <v>0.1917275620408163</v>
       </c>
       <c r="P24">
-        <v>0.9073005804081634</v>
+        <v>0.8734255604081631</v>
       </c>
       <c r="Q24">
-        <v>4.157300580408164</v>
+        <v>4.123425560408164</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09626603028474509</v>
+        <v>0.09682562051005017</v>
       </c>
       <c r="T24">
-        <v>0.8509297711904241</v>
+        <v>0.8603652663084776</v>
       </c>
       <c r="U24">
         <v>0.07580000000000001</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.21744387082571</v>
+        <v>2.121033267746331</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08885160779273862</v>
+        <v>0.08894139196337611</v>
       </c>
       <c r="C25">
-        <v>41.51354941221925</v>
+        <v>40.91009974202927</v>
       </c>
       <c r="D25">
-        <v>49.65854941221924</v>
+        <v>49.60009974202928</v>
       </c>
       <c r="E25">
-        <v>-6.465</v>
+        <v>-5.919999999999998</v>
       </c>
       <c r="F25">
-        <v>12.535</v>
+        <v>13.08</v>
       </c>
       <c r="G25">
         <v>4.39</v>
@@ -3337,28 +3337,28 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M25">
-        <v>0.9501530000000001</v>
+        <v>0.9914640000000002</v>
       </c>
       <c r="N25">
-        <v>1.065153122448979</v>
+        <v>1.02384212244898</v>
       </c>
       <c r="O25">
-        <v>0.1917275620408163</v>
+        <v>0.1842915820408163</v>
       </c>
       <c r="P25">
-        <v>0.8734255604081631</v>
+        <v>0.8395505404081632</v>
       </c>
       <c r="Q25">
-        <v>4.123425560408164</v>
+        <v>4.089550540408164</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09682562051005017</v>
+        <v>0.09739993679391593</v>
       </c>
       <c r="T25">
-        <v>0.8603652663084776</v>
+        <v>0.8700490639296379</v>
       </c>
       <c r="U25">
         <v>0.07580000000000001</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.121033267746331</v>
+        <v>2.032656881590233</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08894139196337608</v>
+        <v>0.09194217613401354</v>
       </c>
       <c r="C26">
-        <v>40.9100997420293</v>
+        <v>38.487736295007</v>
       </c>
       <c r="D26">
-        <v>49.60009974202929</v>
+        <v>47.722736295007</v>
       </c>
       <c r="E26">
-        <v>-5.92</v>
+        <v>-5.375</v>
       </c>
       <c r="F26">
-        <v>13.08</v>
+        <v>13.625</v>
       </c>
       <c r="G26">
         <v>4.39</v>
@@ -3419,45 +3419,45 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M26">
-        <v>0.9914640000000001</v>
+        <v>1.22625</v>
       </c>
       <c r="N26">
-        <v>1.02384212244898</v>
+        <v>0.7890561224489796</v>
       </c>
       <c r="O26">
-        <v>0.1842915820408163</v>
+        <v>0.1420301020408163</v>
       </c>
       <c r="P26">
-        <v>0.8395505404081632</v>
+        <v>0.6470260204081633</v>
       </c>
       <c r="Q26">
-        <v>4.089550540408164</v>
+        <v>3.897026020408163</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0973999367939159</v>
+        <v>0.09798956817868473</v>
       </c>
       <c r="T26">
-        <v>0.8700490639296377</v>
+        <v>0.8799910961540288</v>
       </c>
       <c r="U26">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V26">
         <v>0.18</v>
       </c>
       <c r="W26">
-        <v>0.06215600000000001</v>
+        <v>0.0738</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.032656881590234</v>
+        <v>1.64347084399509</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09194217613401354</v>
+        <v>0.092148400304651</v>
       </c>
       <c r="C27">
-        <v>38.487736295007</v>
+        <v>37.81892286972978</v>
       </c>
       <c r="D27">
-        <v>47.722736295007</v>
+        <v>47.59892286972978</v>
       </c>
       <c r="E27">
-        <v>-5.375</v>
+        <v>-4.83</v>
       </c>
       <c r="F27">
-        <v>13.625</v>
+        <v>14.17</v>
       </c>
       <c r="G27">
         <v>4.39</v>
@@ -3501,28 +3501,28 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M27">
-        <v>1.22625</v>
+        <v>1.2753</v>
       </c>
       <c r="N27">
-        <v>0.7890561224489796</v>
+        <v>0.7400061224489798</v>
       </c>
       <c r="O27">
-        <v>0.1420301020408163</v>
+        <v>0.1332011020408164</v>
       </c>
       <c r="P27">
-        <v>0.6470260204081633</v>
+        <v>0.6068050204081634</v>
       </c>
       <c r="Q27">
-        <v>3.897026020408163</v>
+        <v>3.856805020408164</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09798956817868473</v>
+        <v>0.0985951355468257</v>
       </c>
       <c r="T27">
-        <v>0.8799910961540288</v>
+        <v>0.890201831952052</v>
       </c>
       <c r="U27">
         <v>0.09</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>1.64347084399509</v>
+        <v>1.580260426918356</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.092148400304651</v>
+        <v>0.09235462447528847</v>
       </c>
       <c r="C28">
-        <v>37.81892286972978</v>
+        <v>37.15075023315597</v>
       </c>
       <c r="D28">
-        <v>47.59892286972978</v>
+        <v>47.47575023315597</v>
       </c>
       <c r="E28">
-        <v>-4.83</v>
+        <v>-4.284999999999998</v>
       </c>
       <c r="F28">
-        <v>14.17</v>
+        <v>14.715</v>
       </c>
       <c r="G28">
         <v>4.39</v>
@@ -3583,28 +3583,28 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M28">
-        <v>1.2753</v>
+        <v>1.32435</v>
       </c>
       <c r="N28">
-        <v>0.7400061224489798</v>
+        <v>0.6909561224489795</v>
       </c>
       <c r="O28">
-        <v>0.1332011020408164</v>
+        <v>0.1243721020408163</v>
       </c>
       <c r="P28">
-        <v>0.6068050204081634</v>
+        <v>0.5665840204081632</v>
       </c>
       <c r="Q28">
-        <v>3.856805020408164</v>
+        <v>3.816584020408163</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0985951355468257</v>
+        <v>0.09921729380176503</v>
       </c>
       <c r="T28">
-        <v>0.890201831952052</v>
+        <v>0.9006923139363225</v>
       </c>
       <c r="U28">
         <v>0.09</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>1.580260426918356</v>
+        <v>1.521732262958417</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09235462447528847</v>
+        <v>0.1065521433202307</v>
       </c>
       <c r="C29">
-        <v>37.15075023315597</v>
+        <v>29.42680535878202</v>
       </c>
       <c r="D29">
-        <v>47.47575023315597</v>
+        <v>40.29680535878202</v>
       </c>
       <c r="E29">
-        <v>-4.284999999999998</v>
+        <v>-3.739999999999998</v>
       </c>
       <c r="F29">
-        <v>14.715</v>
+        <v>15.26</v>
       </c>
       <c r="G29">
         <v>4.39</v>
@@ -3665,45 +3665,45 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M29">
-        <v>1.32435</v>
+        <v>2.240168000000001</v>
       </c>
       <c r="N29">
-        <v>0.6909561224489795</v>
+        <v>-0.2248618775510209</v>
       </c>
       <c r="O29">
-        <v>0.1243721020408163</v>
+        <v>-0.04047513795918377</v>
       </c>
       <c r="P29">
-        <v>0.5665840204081632</v>
+        <v>-0.1843867395918372</v>
       </c>
       <c r="Q29">
-        <v>3.816584020408163</v>
+        <v>3.065613260408163</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09921729380176503</v>
+        <v>0.1001447225533483</v>
       </c>
       <c r="T29">
-        <v>0.9006923139363225</v>
+        <v>0.9163300950522023</v>
       </c>
       <c r="U29">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V29">
-        <v>0.18</v>
+        <v>0.1619320970752266</v>
       </c>
       <c r="W29">
-        <v>0.0738</v>
+        <v>0.1230283681493567</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y29">
-        <v>1.521732262958417</v>
+        <v>0.8996227615290368</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1065521433202307</v>
+        <v>0.1075621433202307</v>
       </c>
       <c r="C30">
-        <v>29.42680535878202</v>
+        <v>28.45293948203557</v>
       </c>
       <c r="D30">
-        <v>40.29680535878202</v>
+        <v>39.86793948203557</v>
       </c>
       <c r="E30">
-        <v>-3.739999999999998</v>
+        <v>-3.194999999999999</v>
       </c>
       <c r="F30">
-        <v>15.26</v>
+        <v>15.805</v>
       </c>
       <c r="G30">
         <v>4.39</v>
@@ -3747,37 +3747,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M30">
-        <v>2.240168000000001</v>
+        <v>2.320174000000001</v>
       </c>
       <c r="N30">
-        <v>-0.2248618775510209</v>
+        <v>-0.304867877551021</v>
       </c>
       <c r="O30">
-        <v>-0.04047513795918377</v>
+        <v>-0.05487621795918377</v>
       </c>
       <c r="P30">
-        <v>-0.1843867395918372</v>
+        <v>-0.2499916595918372</v>
       </c>
       <c r="Q30">
-        <v>3.065613260408163</v>
+        <v>3.000008340408163</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1001447225533483</v>
+        <v>0.1009101411808603</v>
       </c>
       <c r="T30">
-        <v>0.9163300950522023</v>
+        <v>0.9292361527289938</v>
       </c>
       <c r="U30">
         <v>0.1468</v>
       </c>
       <c r="V30">
-        <v>0.1619320970752266</v>
+        <v>0.1563482316588395</v>
       </c>
       <c r="W30">
-        <v>0.1230283681493567</v>
+        <v>0.1238480795924824</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.8996227615290368</v>
+        <v>0.8686012869935527</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1075621433202307</v>
+        <v>0.1085721433202307</v>
       </c>
       <c r="C31">
-        <v>28.45293948203557</v>
+        <v>27.48810603788789</v>
       </c>
       <c r="D31">
-        <v>39.86793948203557</v>
+        <v>39.44810603788789</v>
       </c>
       <c r="E31">
-        <v>-3.195</v>
+        <v>-2.650000000000002</v>
       </c>
       <c r="F31">
-        <v>15.805</v>
+        <v>16.35</v>
       </c>
       <c r="G31">
         <v>4.39</v>
@@ -3829,37 +3829,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M31">
-        <v>2.320174</v>
+        <v>2.40018</v>
       </c>
       <c r="N31">
-        <v>-0.3048678775510205</v>
+        <v>-0.3848738775510201</v>
       </c>
       <c r="O31">
-        <v>-0.05487621795918369</v>
+        <v>-0.06927729795918361</v>
       </c>
       <c r="P31">
-        <v>-0.2499916595918368</v>
+        <v>-0.3155965795918365</v>
       </c>
       <c r="Q31">
-        <v>3.000008340408163</v>
+        <v>2.934403420408163</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1009101411808603</v>
+        <v>0.1016974289120154</v>
       </c>
       <c r="T31">
-        <v>0.9292361527289938</v>
+        <v>0.9425109549108367</v>
       </c>
       <c r="U31">
         <v>0.1468</v>
       </c>
       <c r="V31">
-        <v>0.1563482316588395</v>
+        <v>0.1511366239368782</v>
       </c>
       <c r="W31">
-        <v>0.1238480795924824</v>
+        <v>0.1246131436060663</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.8686012869935529</v>
+        <v>0.8396479107604345</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1085721433202307</v>
+        <v>0.1095821433202307</v>
       </c>
       <c r="C32">
-        <v>27.48810603788789</v>
+        <v>26.53202264905589</v>
       </c>
       <c r="D32">
-        <v>39.44810603788789</v>
+        <v>39.03702264905589</v>
       </c>
       <c r="E32">
-        <v>-2.650000000000002</v>
+        <v>-2.105</v>
       </c>
       <c r="F32">
-        <v>16.35</v>
+        <v>16.895</v>
       </c>
       <c r="G32">
         <v>4.39</v>
@@ -3911,37 +3911,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M32">
-        <v>2.40018</v>
+        <v>2.480186</v>
       </c>
       <c r="N32">
-        <v>-0.3848738775510201</v>
+        <v>-0.4648798775510206</v>
       </c>
       <c r="O32">
-        <v>-0.06927729795918361</v>
+        <v>-0.0836783779591837</v>
       </c>
       <c r="P32">
-        <v>-0.3155965795918365</v>
+        <v>-0.3812014995918369</v>
       </c>
       <c r="Q32">
-        <v>2.934403420408163</v>
+        <v>2.868798500408163</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1016974289120154</v>
+        <v>0.102507536577407</v>
       </c>
       <c r="T32">
-        <v>0.9425109549108367</v>
+        <v>0.9561705339675154</v>
       </c>
       <c r="U32">
         <v>0.1468</v>
       </c>
       <c r="V32">
-        <v>0.1511366239368782</v>
+        <v>0.1462612489711725</v>
       </c>
       <c r="W32">
-        <v>0.1246131436060663</v>
+        <v>0.1253288486510319</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.8396479107604345</v>
+        <v>0.8125624942842914</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1095821433202307</v>
+        <v>0.1283719046150613</v>
       </c>
       <c r="C33">
-        <v>26.53202264905589</v>
+        <v>19.64796887020495</v>
       </c>
       <c r="D33">
-        <v>39.03702264905589</v>
+        <v>32.69796887020495</v>
       </c>
       <c r="E33">
-        <v>-2.105</v>
+        <v>-1.559999999999999</v>
       </c>
       <c r="F33">
-        <v>16.895</v>
+        <v>17.44</v>
       </c>
       <c r="G33">
         <v>4.39</v>
@@ -3993,45 +3993,45 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M33">
-        <v>2.480186</v>
+        <v>3.501952</v>
       </c>
       <c r="N33">
-        <v>-0.4648798775510206</v>
+        <v>-1.486645877551021</v>
       </c>
       <c r="O33">
-        <v>-0.0836783779591837</v>
+        <v>-0.2675962579591837</v>
       </c>
       <c r="P33">
-        <v>-0.3812014995918369</v>
+        <v>-1.219049619591837</v>
       </c>
       <c r="Q33">
-        <v>2.868798500408163</v>
+        <v>2.030950380408163</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.102507536577407</v>
+        <v>0.1040764140194726</v>
       </c>
       <c r="T33">
-        <v>0.9561705339675154</v>
+        <v>0.9826240615239769</v>
       </c>
       <c r="U33">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.1462612489711725</v>
+        <v>0.1035865431738688</v>
       </c>
       <c r="W33">
-        <v>0.1253288486510319</v>
+        <v>0.1799998221306871</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y33">
-        <v>0.8125624942842914</v>
+        <v>0.5754807954103824</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1283719046150613</v>
+        <v>0.1299219046150612</v>
       </c>
       <c r="C34">
-        <v>19.64796887020495</v>
+        <v>18.67075370668391</v>
       </c>
       <c r="D34">
-        <v>32.69796887020495</v>
+        <v>32.26575370668391</v>
       </c>
       <c r="E34">
-        <v>-1.559999999999999</v>
+        <v>-1.015000000000001</v>
       </c>
       <c r="F34">
-        <v>17.44</v>
+        <v>17.985</v>
       </c>
       <c r="G34">
         <v>4.39</v>
@@ -4075,37 +4075,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M34">
-        <v>3.501952</v>
+        <v>3.611388</v>
       </c>
       <c r="N34">
-        <v>-1.486645877551021</v>
+        <v>-1.59608187755102</v>
       </c>
       <c r="O34">
-        <v>-0.2675962579591837</v>
+        <v>-0.2872947379591836</v>
       </c>
       <c r="P34">
-        <v>-1.219049619591837</v>
+        <v>-1.308787139591836</v>
       </c>
       <c r="Q34">
-        <v>2.030950380408163</v>
+        <v>1.941212860408164</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1040764140194726</v>
+        <v>0.1049462112436438</v>
       </c>
       <c r="T34">
-        <v>0.9826240615239769</v>
+        <v>0.9972900922929914</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.1035865431738688</v>
+        <v>0.100447557017085</v>
       </c>
       <c r="W34">
-        <v>0.1799998221306871</v>
+        <v>0.1806301305509694</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.5754807954103824</v>
+        <v>0.5580419834282497</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1299219046150612</v>
+        <v>0.1314719046150613</v>
       </c>
       <c r="C35">
-        <v>18.67075370668391</v>
+        <v>17.70481586944558</v>
       </c>
       <c r="D35">
-        <v>32.26575370668391</v>
+        <v>31.84481586944558</v>
       </c>
       <c r="E35">
-        <v>-1.015000000000001</v>
+        <v>-0.4699999999999989</v>
       </c>
       <c r="F35">
-        <v>17.985</v>
+        <v>18.53</v>
       </c>
       <c r="G35">
         <v>4.39</v>
@@ -4157,37 +4157,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M35">
-        <v>3.611388</v>
+        <v>3.720824</v>
       </c>
       <c r="N35">
-        <v>-1.59608187755102</v>
+        <v>-1.705517877551021</v>
       </c>
       <c r="O35">
-        <v>-0.2872947379591836</v>
+        <v>-0.3069932179591837</v>
       </c>
       <c r="P35">
-        <v>-1.308787139591836</v>
+        <v>-1.398524659591837</v>
       </c>
       <c r="Q35">
-        <v>1.941212860408164</v>
+        <v>1.851475340408163</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1049462112436438</v>
+        <v>0.1058423659594566</v>
       </c>
       <c r="T35">
-        <v>0.9972900922929914</v>
+        <v>1.012400548236825</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.100447557017085</v>
+        <v>0.09749321710481773</v>
       </c>
       <c r="W35">
-        <v>0.1806301305509694</v>
+        <v>0.1812233620053526</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.5580419834282497</v>
+        <v>0.5416289839156541</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1314719046150613</v>
+        <v>0.1330219046150612</v>
       </c>
       <c r="C36">
-        <v>17.70481586944558</v>
+        <v>16.74971967169105</v>
       </c>
       <c r="D36">
-        <v>31.84481586944558</v>
+        <v>31.43471967169106</v>
       </c>
       <c r="E36">
-        <v>-0.4699999999999989</v>
+        <v>0.07500000000000284</v>
       </c>
       <c r="F36">
-        <v>18.53</v>
+        <v>19.075</v>
       </c>
       <c r="G36">
         <v>4.39</v>
@@ -4239,37 +4239,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M36">
-        <v>3.720824</v>
+        <v>3.830260000000001</v>
       </c>
       <c r="N36">
-        <v>-1.705517877551021</v>
+        <v>-1.814953877551021</v>
       </c>
       <c r="O36">
-        <v>-0.3069932179591837</v>
+        <v>-0.3266916979591838</v>
       </c>
       <c r="P36">
-        <v>-1.398524659591837</v>
+        <v>-1.488262179591837</v>
       </c>
       <c r="Q36">
-        <v>1.851475340408163</v>
+        <v>1.761737820408163</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1058423659594566</v>
+        <v>0.1067660946665252</v>
       </c>
       <c r="T36">
-        <v>1.012400548236825</v>
+        <v>1.027975941286622</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.09749321710481773</v>
+        <v>0.09470769661610863</v>
       </c>
       <c r="W36">
-        <v>0.1812233620053526</v>
+        <v>0.1817826945194854</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.5416289839156541</v>
+        <v>0.5261538700894924</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1330219046150612</v>
+        <v>0.1345719046150612</v>
       </c>
       <c r="C37">
-        <v>16.74971967169105</v>
+        <v>15.80505158430077</v>
       </c>
       <c r="D37">
-        <v>31.43471967169106</v>
+        <v>31.03505158430078</v>
       </c>
       <c r="E37">
-        <v>0.07500000000000284</v>
+        <v>0.620000000000001</v>
       </c>
       <c r="F37">
-        <v>19.075</v>
+        <v>19.62</v>
       </c>
       <c r="G37">
         <v>4.39</v>
@@ -4321,37 +4321,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M37">
-        <v>3.830260000000001</v>
+        <v>3.939696000000001</v>
       </c>
       <c r="N37">
-        <v>-1.814953877551021</v>
+        <v>-1.924389877551021</v>
       </c>
       <c r="O37">
-        <v>-0.3266916979591838</v>
+        <v>-0.3463901779591838</v>
       </c>
       <c r="P37">
-        <v>-1.488262179591837</v>
+        <v>-1.577999699591837</v>
       </c>
       <c r="Q37">
-        <v>1.761737820408163</v>
+        <v>1.672000300408163</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1067660946665252</v>
+        <v>0.1077186898956896</v>
       </c>
       <c r="T37">
-        <v>1.027975941286622</v>
+        <v>1.044038065369225</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.09470769661610863</v>
+        <v>0.09207692726566118</v>
       </c>
       <c r="W37">
-        <v>0.1817826945194854</v>
+        <v>0.1823109530050552</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.5261538700894924</v>
+        <v>0.5115384848092288</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1345719046150612</v>
+        <v>0.1492735643339724</v>
       </c>
       <c r="C38">
-        <v>15.80505158430077</v>
+        <v>11.92018705475674</v>
       </c>
       <c r="D38">
-        <v>31.03505158430078</v>
+        <v>27.69518705475674</v>
       </c>
       <c r="E38">
-        <v>0.620000000000001</v>
+        <v>1.164999999999999</v>
       </c>
       <c r="F38">
-        <v>19.62</v>
+        <v>20.165</v>
       </c>
       <c r="G38">
         <v>4.39</v>
@@ -4403,45 +4403,45 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M38">
-        <v>3.939696000000001</v>
+        <v>4.754907</v>
       </c>
       <c r="N38">
-        <v>-1.924389877551021</v>
+        <v>-2.739600877551021</v>
       </c>
       <c r="O38">
-        <v>-0.3463901779591838</v>
+        <v>-0.4931281579591837</v>
       </c>
       <c r="P38">
-        <v>-1.577999699591837</v>
+        <v>-2.246472719591837</v>
       </c>
       <c r="Q38">
-        <v>1.672000300408163</v>
+        <v>1.003527280408163</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1077186898956896</v>
+        <v>0.1090216210351627</v>
       </c>
       <c r="T38">
-        <v>1.044038065369225</v>
+        <v>1.066007356199771</v>
       </c>
       <c r="U38">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.09207692726566118</v>
+        <v>0.07629068287577787</v>
       </c>
       <c r="W38">
-        <v>0.1823109530050552</v>
+        <v>0.2178106569778916</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.5115384848092288</v>
+        <v>0.4238371270876549</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1492735643339724</v>
+        <v>0.1511735643339724</v>
       </c>
       <c r="C39">
-        <v>11.92018705475674</v>
+        <v>10.99528697738432</v>
       </c>
       <c r="D39">
-        <v>27.69518705475674</v>
+        <v>27.31528697738432</v>
       </c>
       <c r="E39">
-        <v>1.164999999999999</v>
+        <v>1.710000000000001</v>
       </c>
       <c r="F39">
-        <v>20.165</v>
+        <v>20.71</v>
       </c>
       <c r="G39">
         <v>4.39</v>
@@ -4485,37 +4485,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M39">
-        <v>4.754907</v>
+        <v>4.883418000000001</v>
       </c>
       <c r="N39">
-        <v>-2.739600877551021</v>
+        <v>-2.868111877551021</v>
       </c>
       <c r="O39">
-        <v>-0.4931281579591837</v>
+        <v>-0.5162601379591838</v>
       </c>
       <c r="P39">
-        <v>-2.246472719591837</v>
+        <v>-2.351851739591837</v>
       </c>
       <c r="Q39">
-        <v>1.003527280408163</v>
+        <v>0.8981482604081625</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1090216210351627</v>
+        <v>0.110041324600246</v>
       </c>
       <c r="T39">
-        <v>1.066007356199771</v>
+        <v>1.083201023235252</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.07629068287577787</v>
+        <v>0.07428303332641528</v>
       </c>
       <c r="W39">
-        <v>0.2178106569778916</v>
+        <v>0.2182840607416313</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.4238371270876549</v>
+        <v>0.4126835184800849</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1511735643339724</v>
+        <v>0.1530735643339724</v>
       </c>
       <c r="C40">
-        <v>10.99528697738432</v>
+        <v>10.08066819090218</v>
       </c>
       <c r="D40">
-        <v>27.31528697738432</v>
+        <v>26.94566819090218</v>
       </c>
       <c r="E40">
-        <v>1.710000000000001</v>
+        <v>2.254999999999999</v>
       </c>
       <c r="F40">
-        <v>20.71</v>
+        <v>21.255</v>
       </c>
       <c r="G40">
         <v>4.39</v>
@@ -4567,37 +4567,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M40">
-        <v>4.883418000000001</v>
+        <v>5.011929</v>
       </c>
       <c r="N40">
-        <v>-2.868111877551021</v>
+        <v>-2.996622877551021</v>
       </c>
       <c r="O40">
-        <v>-0.5162601379591838</v>
+        <v>-0.5393921179591837</v>
       </c>
       <c r="P40">
-        <v>-2.351851739591837</v>
+        <v>-2.457230759591837</v>
       </c>
       <c r="Q40">
-        <v>0.8981482604081625</v>
+        <v>0.792769240408163</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.110041324600246</v>
+        <v>0.1110944610691025</v>
       </c>
       <c r="T40">
-        <v>1.083201023235252</v>
+        <v>1.10095841705878</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.07428303332641528</v>
+        <v>0.07237834016419951</v>
       </c>
       <c r="W40">
-        <v>0.2182840607416313</v>
+        <v>0.2187331873892818</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4126835184800849</v>
+        <v>0.4021018898011084</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1530735643339724</v>
+        <v>0.1549735643339724</v>
       </c>
       <c r="C41">
-        <v>10.08066819090218</v>
+        <v>9.175918901429405</v>
       </c>
       <c r="D41">
-        <v>26.94566819090218</v>
+        <v>26.58591890142941</v>
       </c>
       <c r="E41">
-        <v>2.254999999999999</v>
+        <v>2.800000000000001</v>
       </c>
       <c r="F41">
-        <v>21.255</v>
+        <v>21.8</v>
       </c>
       <c r="G41">
         <v>4.39</v>
@@ -4649,37 +4649,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M41">
-        <v>5.011929</v>
+        <v>5.140440000000001</v>
       </c>
       <c r="N41">
-        <v>-2.996622877551021</v>
+        <v>-3.125133877551021</v>
       </c>
       <c r="O41">
-        <v>-0.5393921179591837</v>
+        <v>-0.5625240979591838</v>
       </c>
       <c r="P41">
-        <v>-2.457230759591837</v>
+        <v>-2.562609779591837</v>
       </c>
       <c r="Q41">
-        <v>0.792769240408163</v>
+        <v>0.6873902204081626</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1110944610691025</v>
+        <v>0.1121827020869209</v>
       </c>
       <c r="T41">
-        <v>1.10095841705878</v>
+        <v>1.11930772400976</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.07237834016419951</v>
+        <v>0.07056888166009452</v>
       </c>
       <c r="W41">
-        <v>0.2187331873892818</v>
+        <v>0.2191598577045497</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.4021018898011084</v>
+        <v>0.3920493425560807</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1549735643339724</v>
+        <v>0.1568735643339724</v>
       </c>
       <c r="C42">
-        <v>9.175918901429405</v>
+        <v>8.280649016647605</v>
       </c>
       <c r="D42">
-        <v>26.58591890142941</v>
+        <v>26.23564901664761</v>
       </c>
       <c r="E42">
-        <v>2.800000000000001</v>
+        <v>3.345000000000002</v>
       </c>
       <c r="F42">
-        <v>21.8</v>
+        <v>22.345</v>
       </c>
       <c r="G42">
         <v>4.39</v>
@@ -4731,37 +4731,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M42">
-        <v>5.140440000000001</v>
+        <v>5.268951</v>
       </c>
       <c r="N42">
-        <v>-3.125133877551021</v>
+        <v>-3.253644877551021</v>
       </c>
       <c r="O42">
-        <v>-0.5625240979591838</v>
+        <v>-0.5856560779591837</v>
       </c>
       <c r="P42">
-        <v>-2.562609779591837</v>
+        <v>-2.667988799591837</v>
       </c>
       <c r="Q42">
-        <v>0.6873902204081626</v>
+        <v>0.582011200408163</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1121827020869209</v>
+        <v>0.1133078326307669</v>
       </c>
       <c r="T42">
-        <v>1.11930772400976</v>
+        <v>1.138279041365857</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.07056888166009452</v>
+        <v>0.06884768942448247</v>
       </c>
       <c r="W42">
-        <v>0.2191598577045497</v>
+        <v>0.219565714833707</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3920493425560807</v>
+        <v>0.3824871634693471</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1568735643339724</v>
+        <v>0.1587735643339724</v>
       </c>
       <c r="C43">
-        <v>8.280649016647605</v>
+        <v>7.394488734798784</v>
       </c>
       <c r="D43">
-        <v>26.23564901664761</v>
+        <v>25.89448873479878</v>
       </c>
       <c r="E43">
-        <v>3.345000000000002</v>
+        <v>3.890000000000001</v>
       </c>
       <c r="F43">
-        <v>22.345</v>
+        <v>22.89</v>
       </c>
       <c r="G43">
         <v>4.39</v>
@@ -4813,37 +4813,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M43">
-        <v>5.268951</v>
+        <v>5.397462</v>
       </c>
       <c r="N43">
-        <v>-3.253644877551021</v>
+        <v>-3.38215587755102</v>
       </c>
       <c r="O43">
-        <v>-0.5856560779591837</v>
+        <v>-0.6087880579591837</v>
       </c>
       <c r="P43">
-        <v>-2.667988799591837</v>
+        <v>-2.773367819591837</v>
       </c>
       <c r="Q43">
-        <v>0.582011200408163</v>
+        <v>0.4766321804081635</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1133078326307669</v>
+        <v>0.1144717607795733</v>
       </c>
       <c r="T43">
-        <v>1.138279041365857</v>
+        <v>1.157904542079062</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.06884768942448247</v>
+        <v>0.06720845872389955</v>
       </c>
       <c r="W43">
-        <v>0.219565714833707</v>
+        <v>0.2199522454329045</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3824871634693471</v>
+        <v>0.3733803262438864</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1587735643339724</v>
+        <v>0.1606735643339724</v>
       </c>
       <c r="C44">
-        <v>7.394488734798784</v>
+        <v>6.517087242359473</v>
       </c>
       <c r="D44">
-        <v>25.89448873479878</v>
+        <v>25.56208724235947</v>
       </c>
       <c r="E44">
-        <v>3.890000000000001</v>
+        <v>4.434999999999999</v>
       </c>
       <c r="F44">
-        <v>22.89</v>
+        <v>23.435</v>
       </c>
       <c r="G44">
         <v>4.39</v>
@@ -4895,37 +4895,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M44">
-        <v>5.397462</v>
+        <v>5.525973</v>
       </c>
       <c r="N44">
-        <v>-3.38215587755102</v>
+        <v>-3.51066687755102</v>
       </c>
       <c r="O44">
-        <v>-0.6087880579591837</v>
+        <v>-0.6319200379591836</v>
       </c>
       <c r="P44">
-        <v>-2.773367819591837</v>
+        <v>-2.878746839591837</v>
       </c>
       <c r="Q44">
-        <v>0.4766321804081635</v>
+        <v>0.3712531604081635</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1144717607795733</v>
+        <v>0.1156765285125483</v>
       </c>
       <c r="T44">
-        <v>1.157904542079062</v>
+        <v>1.178218656852379</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.06720845872389955</v>
+        <v>0.06564547131171584</v>
       </c>
       <c r="W44">
-        <v>0.2199522454329045</v>
+        <v>0.2203207978646974</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3733803262438864</v>
+        <v>0.3646970628428658</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1606735643339724</v>
+        <v>0.1625735643339724</v>
       </c>
       <c r="C45">
-        <v>6.517087242359473</v>
+        <v>5.648111510749484</v>
       </c>
       <c r="D45">
-        <v>25.56208724235947</v>
+        <v>25.23811151074948</v>
       </c>
       <c r="E45">
-        <v>4.434999999999999</v>
+        <v>4.98</v>
       </c>
       <c r="F45">
-        <v>23.435</v>
+        <v>23.98</v>
       </c>
       <c r="G45">
         <v>4.39</v>
@@ -4977,37 +4977,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M45">
-        <v>5.525973</v>
+        <v>5.654484</v>
       </c>
       <c r="N45">
-        <v>-3.51066687755102</v>
+        <v>-3.63917787755102</v>
       </c>
       <c r="O45">
-        <v>-0.6319200379591836</v>
+        <v>-0.6550520179591837</v>
       </c>
       <c r="P45">
-        <v>-2.878746839591837</v>
+        <v>-2.984125859591837</v>
       </c>
       <c r="Q45">
-        <v>0.3712531604081635</v>
+        <v>0.2658741404081635</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1156765285125483</v>
+        <v>0.116924323664558</v>
       </c>
       <c r="T45">
-        <v>1.178218656852379</v>
+        <v>1.199258275724743</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.06564547131171584</v>
+        <v>0.06415352878190411</v>
       </c>
       <c r="W45">
-        <v>0.2203207978646974</v>
+        <v>0.220672597913227</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3646970628428658</v>
+        <v>0.3564084932328007</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1625735643339724</v>
+        <v>0.1644735643339724</v>
       </c>
       <c r="C46">
-        <v>5.648111510749484</v>
+        <v>4.787245183399062</v>
       </c>
       <c r="D46">
-        <v>25.23811151074948</v>
+        <v>24.92224518339906</v>
       </c>
       <c r="E46">
-        <v>4.98</v>
+        <v>5.525000000000002</v>
       </c>
       <c r="F46">
-        <v>23.98</v>
+        <v>24.525</v>
       </c>
       <c r="G46">
         <v>4.39</v>
@@ -5059,37 +5059,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M46">
-        <v>5.654484</v>
+        <v>5.782995000000001</v>
       </c>
       <c r="N46">
-        <v>-3.63917787755102</v>
+        <v>-3.767688877551021</v>
       </c>
       <c r="O46">
-        <v>-0.6550520179591837</v>
+        <v>-0.6781839979591837</v>
       </c>
       <c r="P46">
-        <v>-2.984125859591837</v>
+        <v>-3.089504879591837</v>
       </c>
       <c r="Q46">
-        <v>0.2658741404081635</v>
+        <v>0.1604951204081626</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.116924323664558</v>
+        <v>0.1182174931857318</v>
       </c>
       <c r="T46">
-        <v>1.199258275724743</v>
+        <v>1.221062971647011</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.06415352878190411</v>
+        <v>0.06272789480897291</v>
       </c>
       <c r="W46">
-        <v>0.220672597913227</v>
+        <v>0.2210087624040442</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3564084932328007</v>
+        <v>0.3484883044942939</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1644735643339724</v>
+        <v>0.1663735643339724</v>
       </c>
       <c r="C47">
-        <v>4.787245183399062</v>
+        <v>3.934187545356121</v>
       </c>
       <c r="D47">
-        <v>24.92224518339906</v>
+        <v>24.61418754535612</v>
       </c>
       <c r="E47">
-        <v>5.525000000000002</v>
+        <v>6.07</v>
       </c>
       <c r="F47">
-        <v>24.525</v>
+        <v>25.07</v>
       </c>
       <c r="G47">
         <v>4.39</v>
@@ -5141,37 +5141,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M47">
-        <v>5.782995000000001</v>
+        <v>5.911506</v>
       </c>
       <c r="N47">
-        <v>-3.767688877551021</v>
+        <v>-3.89619987755102</v>
       </c>
       <c r="O47">
-        <v>-0.6781839979591837</v>
+        <v>-0.7013159779591837</v>
       </c>
       <c r="P47">
-        <v>-3.089504879591837</v>
+        <v>-3.194883899591837</v>
       </c>
       <c r="Q47">
-        <v>0.1604951204081626</v>
+        <v>0.05511610040816306</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1182174931857318</v>
+        <v>0.1195585578743565</v>
       </c>
       <c r="T47">
-        <v>1.221062971647011</v>
+        <v>1.243675248899733</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.06272789480897291</v>
+        <v>0.06136424492182133</v>
       </c>
       <c r="W47">
-        <v>0.2210087624040442</v>
+        <v>0.2213303110474345</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3484883044942939</v>
+        <v>0.3409124717878963</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1663735643339724</v>
+        <v>0.1682735643339724</v>
       </c>
       <c r="C48">
-        <v>3.934187545356121</v>
+        <v>3.088652568378965</v>
       </c>
       <c r="D48">
-        <v>24.61418754535612</v>
+        <v>24.31365256837897</v>
       </c>
       <c r="E48">
-        <v>6.07</v>
+        <v>6.615000000000002</v>
       </c>
       <c r="F48">
-        <v>25.07</v>
+        <v>25.615</v>
       </c>
       <c r="G48">
         <v>4.39</v>
@@ -5223,37 +5223,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M48">
-        <v>5.911506</v>
+        <v>6.040017000000001</v>
       </c>
       <c r="N48">
-        <v>-3.89619987755102</v>
+        <v>-4.024710877551021</v>
       </c>
       <c r="O48">
-        <v>-0.7013159779591837</v>
+        <v>-0.7244479579591837</v>
       </c>
       <c r="P48">
-        <v>-3.194883899591837</v>
+        <v>-3.300262919591837</v>
       </c>
       <c r="Q48">
-        <v>0.05511610040816306</v>
+        <v>-0.05026291959183737</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1195585578743565</v>
+        <v>0.1209502287776462</v>
       </c>
       <c r="T48">
-        <v>1.243675248899733</v>
+        <v>1.26714081963369</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.06136424492182133</v>
+        <v>0.06005862268944214</v>
       </c>
       <c r="W48">
-        <v>0.2213303110474345</v>
+        <v>0.2216381767698296</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3409124717878963</v>
+        <v>0.3336590149413453</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1682735643339724</v>
+        <v>0.1701735643339724</v>
       </c>
       <c r="C49">
-        <v>3.088652568378965</v>
+        <v>2.250368025140798</v>
       </c>
       <c r="D49">
-        <v>24.31365256837897</v>
+        <v>24.0203680251408</v>
       </c>
       <c r="E49">
-        <v>6.615000000000002</v>
+        <v>7.160000000000004</v>
       </c>
       <c r="F49">
-        <v>25.615</v>
+        <v>26.16</v>
       </c>
       <c r="G49">
         <v>4.39</v>
@@ -5305,37 +5305,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M49">
-        <v>6.040017000000001</v>
+        <v>6.168528000000001</v>
       </c>
       <c r="N49">
-        <v>-4.024710877551021</v>
+        <v>-4.153221877551021</v>
       </c>
       <c r="O49">
-        <v>-0.7244479579591837</v>
+        <v>-0.7475799379591839</v>
       </c>
       <c r="P49">
-        <v>-3.300262919591837</v>
+        <v>-3.405641939591837</v>
       </c>
       <c r="Q49">
-        <v>-0.05026291959183737</v>
+        <v>-0.1556419395918374</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1209502287776462</v>
+        <v>0.1223954254849087</v>
       </c>
       <c r="T49">
-        <v>1.26714081963369</v>
+        <v>1.291508912318954</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.06005862268944214</v>
+        <v>0.0588074013834121</v>
       </c>
       <c r="W49">
-        <v>0.2216381767698296</v>
+        <v>0.2219332147537914</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3336590149413453</v>
+        <v>0.3267077854634005</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1701735643339724</v>
+        <v>0.1720735643339724</v>
       </c>
       <c r="C50">
-        <v>2.250368025140805</v>
+        <v>1.419074666779672</v>
       </c>
       <c r="D50">
-        <v>24.0203680251408</v>
+        <v>23.73407466677967</v>
       </c>
       <c r="E50">
-        <v>7.16</v>
+        <v>7.704999999999998</v>
       </c>
       <c r="F50">
-        <v>26.16</v>
+        <v>26.705</v>
       </c>
       <c r="G50">
         <v>4.39</v>
@@ -5387,37 +5387,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M50">
-        <v>6.168528</v>
+        <v>6.297039</v>
       </c>
       <c r="N50">
-        <v>-4.153221877551021</v>
+        <v>-4.28173287755102</v>
       </c>
       <c r="O50">
-        <v>-0.7475799379591836</v>
+        <v>-0.7707119179591836</v>
       </c>
       <c r="P50">
-        <v>-3.405641939591837</v>
+        <v>-3.511020959591836</v>
       </c>
       <c r="Q50">
-        <v>-0.1556419395918369</v>
+        <v>-0.2610209595918365</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1223954254849086</v>
+        <v>0.123897296572848</v>
       </c>
       <c r="T50">
-        <v>1.291508912318954</v>
+        <v>1.31683261648207</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.05880740138341211</v>
+        <v>0.05760725033477105</v>
       </c>
       <c r="W50">
-        <v>0.2219332147537914</v>
+        <v>0.222216210371061</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3267077854634006</v>
+        <v>0.3200402796376169</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1720735643339724</v>
+        <v>0.1739735643339724</v>
       </c>
       <c r="C51">
-        <v>1.419074666779672</v>
+        <v>0.5945254585713293</v>
       </c>
       <c r="D51">
-        <v>23.73407466677967</v>
+        <v>23.45452545857133</v>
       </c>
       <c r="E51">
-        <v>7.704999999999998</v>
+        <v>8.25</v>
       </c>
       <c r="F51">
-        <v>26.705</v>
+        <v>27.25</v>
       </c>
       <c r="G51">
         <v>4.39</v>
@@ -5469,37 +5469,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M51">
-        <v>6.297039</v>
+        <v>6.42555</v>
       </c>
       <c r="N51">
-        <v>-4.28173287755102</v>
+        <v>-4.410243877551021</v>
       </c>
       <c r="O51">
-        <v>-0.7707119179591836</v>
+        <v>-0.7938438979591836</v>
       </c>
       <c r="P51">
-        <v>-3.511020959591836</v>
+        <v>-3.616399979591837</v>
       </c>
       <c r="Q51">
-        <v>-0.2610209595918365</v>
+        <v>-0.3663999795918369</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.123897296572848</v>
+        <v>0.125459242504305</v>
       </c>
       <c r="T51">
-        <v>1.31683261648207</v>
+        <v>1.343169268811712</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.05760725033477105</v>
+        <v>0.05645510532807562</v>
       </c>
       <c r="W51">
-        <v>0.222216210371061</v>
+        <v>0.2224878861636398</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3200402796376169</v>
+        <v>0.3136394740448646</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1739735643339724</v>
+        <v>0.1758735643339724</v>
       </c>
       <c r="C52">
-        <v>0.5945254585713293</v>
+        <v>-0.2235151310114638</v>
       </c>
       <c r="D52">
-        <v>23.45452545857133</v>
+        <v>23.18148486898854</v>
       </c>
       <c r="E52">
-        <v>8.25</v>
+        <v>8.795000000000002</v>
       </c>
       <c r="F52">
-        <v>27.25</v>
+        <v>27.795</v>
       </c>
       <c r="G52">
         <v>4.39</v>
@@ -5551,37 +5551,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M52">
-        <v>6.42555</v>
+        <v>6.554061000000001</v>
       </c>
       <c r="N52">
-        <v>-4.410243877551021</v>
+        <v>-4.538754877551021</v>
       </c>
       <c r="O52">
-        <v>-0.7938438979591836</v>
+        <v>-0.8169758779591838</v>
       </c>
       <c r="P52">
-        <v>-3.616399979591837</v>
+        <v>-3.721778999591837</v>
       </c>
       <c r="Q52">
-        <v>-0.3663999795918369</v>
+        <v>-0.4717789995918373</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.125459242504305</v>
+        <v>0.1270849413309235</v>
       </c>
       <c r="T52">
-        <v>1.343169268811712</v>
+        <v>1.370580886542563</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.05645510532807562</v>
+        <v>0.05534814247850551</v>
       </c>
       <c r="W52">
-        <v>0.2224878861636398</v>
+        <v>0.2227489080035684</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3136394740448646</v>
+        <v>0.3074896804361417</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1758735643339724</v>
+        <v>0.1777735643339724</v>
       </c>
       <c r="C53">
-        <v>-0.2235151310114638</v>
+        <v>-1.035271792153516</v>
       </c>
       <c r="D53">
-        <v>23.18148486898854</v>
+        <v>22.91472820784648</v>
       </c>
       <c r="E53">
-        <v>8.795000000000002</v>
+        <v>9.34</v>
       </c>
       <c r="F53">
-        <v>27.795</v>
+        <v>28.34</v>
       </c>
       <c r="G53">
         <v>4.39</v>
@@ -5633,37 +5633,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M53">
-        <v>6.554061000000001</v>
+        <v>6.682572</v>
       </c>
       <c r="N53">
-        <v>-4.538754877551021</v>
+        <v>-4.667265877551021</v>
       </c>
       <c r="O53">
-        <v>-0.8169758779591838</v>
+        <v>-0.8401078579591837</v>
       </c>
       <c r="P53">
-        <v>-3.721778999591837</v>
+        <v>-3.827158019591837</v>
       </c>
       <c r="Q53">
-        <v>-0.4717789995918373</v>
+        <v>-0.5771580195918369</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1270849413309235</v>
+        <v>0.128778377608651</v>
       </c>
       <c r="T53">
-        <v>1.370580886542563</v>
+        <v>1.3991346550122</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.05534814247850551</v>
+        <v>0.05428375512314963</v>
       </c>
       <c r="W53">
-        <v>0.2227489080035684</v>
+        <v>0.2229998905419613</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3074896804361417</v>
+        <v>0.3015764173508313</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1777735643339724</v>
+        <v>0.1796735643339724</v>
       </c>
       <c r="C54">
-        <v>-1.035271792153516</v>
+        <v>-1.840958990374673</v>
       </c>
       <c r="D54">
-        <v>22.91472820784648</v>
+        <v>22.65404100962533</v>
       </c>
       <c r="E54">
-        <v>9.34</v>
+        <v>9.885000000000002</v>
       </c>
       <c r="F54">
-        <v>28.34</v>
+        <v>28.885</v>
       </c>
       <c r="G54">
         <v>4.39</v>
@@ -5715,37 +5715,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M54">
-        <v>6.682572</v>
+        <v>6.811083000000001</v>
       </c>
       <c r="N54">
-        <v>-4.667265877551021</v>
+        <v>-4.795776877551021</v>
       </c>
       <c r="O54">
-        <v>-0.8401078579591837</v>
+        <v>-0.8632398379591838</v>
       </c>
       <c r="P54">
-        <v>-3.827158019591837</v>
+        <v>-3.932537039591837</v>
       </c>
       <c r="Q54">
-        <v>-0.5771580195918369</v>
+        <v>-0.6825370395918373</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.128778377608651</v>
+        <v>0.1305438750045798</v>
       </c>
       <c r="T54">
-        <v>1.3991346550122</v>
+        <v>1.428903477459268</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.05428375512314963</v>
+        <v>0.05325953332837322</v>
       </c>
       <c r="W54">
-        <v>0.2229998905419613</v>
+        <v>0.2232414020411696</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3015764173508313</v>
+        <v>0.2958862962687402</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1796735643339724</v>
+        <v>0.1815735643339724</v>
       </c>
       <c r="C55">
-        <v>-1.840958990374673</v>
+        <v>-2.640781541587291</v>
       </c>
       <c r="D55">
-        <v>22.65404100962533</v>
+        <v>22.39921845841271</v>
       </c>
       <c r="E55">
-        <v>9.885000000000002</v>
+        <v>10.43</v>
       </c>
       <c r="F55">
-        <v>28.885</v>
+        <v>29.43</v>
       </c>
       <c r="G55">
         <v>4.39</v>
@@ -5797,37 +5797,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M55">
-        <v>6.811083000000001</v>
+        <v>6.939594000000001</v>
       </c>
       <c r="N55">
-        <v>-4.795776877551021</v>
+        <v>-4.924287877551022</v>
       </c>
       <c r="O55">
-        <v>-0.8632398379591838</v>
+        <v>-0.8863718179591838</v>
       </c>
       <c r="P55">
-        <v>-3.932537039591837</v>
+        <v>-4.037916059591838</v>
       </c>
       <c r="Q55">
-        <v>-0.6825370395918373</v>
+        <v>-0.7879160595918382</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1305438750045798</v>
+        <v>0.1323861331568533</v>
       </c>
       <c r="T55">
-        <v>1.428903477459268</v>
+        <v>1.45996659653447</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.05325953332837322</v>
+        <v>0.05227324567414408</v>
       </c>
       <c r="W55">
-        <v>0.2232414020411696</v>
+        <v>0.2234739686700369</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2958862962687402</v>
+        <v>0.2904069204119116</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1815735643339724</v>
+        <v>0.1834735643339724</v>
       </c>
       <c r="C56">
-        <v>-2.640781541587291</v>
+        <v>-3.434935148774464</v>
       </c>
       <c r="D56">
-        <v>22.39921845841271</v>
+        <v>22.15006485122554</v>
       </c>
       <c r="E56">
-        <v>10.43</v>
+        <v>10.975</v>
       </c>
       <c r="F56">
-        <v>29.43</v>
+        <v>29.975</v>
       </c>
       <c r="G56">
         <v>4.39</v>
@@ -5879,37 +5879,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M56">
-        <v>6.939594000000001</v>
+        <v>7.068105000000001</v>
       </c>
       <c r="N56">
-        <v>-4.924287877551022</v>
+        <v>-5.052798877551021</v>
       </c>
       <c r="O56">
-        <v>-0.8863718179591838</v>
+        <v>-0.9095037979591838</v>
       </c>
       <c r="P56">
-        <v>-4.037916059591838</v>
+        <v>-4.143295079591837</v>
       </c>
       <c r="Q56">
-        <v>-0.7879160595918382</v>
+        <v>-0.8932950795918373</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1323861331568533</v>
+        <v>0.1343102694492278</v>
       </c>
       <c r="T56">
-        <v>1.45996659653447</v>
+        <v>1.49241029867968</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.05227324567414408</v>
+        <v>0.05132282302552329</v>
       </c>
       <c r="W56">
-        <v>0.2234739686700369</v>
+        <v>0.2236980783305816</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2904069204119116</v>
+        <v>0.2851267945862405</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1834735643339724</v>
+        <v>0.1853735643339724</v>
       </c>
       <c r="C57">
-        <v>-3.434935148774464</v>
+        <v>-4.223606903244402</v>
       </c>
       <c r="D57">
-        <v>22.15006485122554</v>
+        <v>21.9063930967556</v>
       </c>
       <c r="E57">
-        <v>10.975</v>
+        <v>11.52</v>
       </c>
       <c r="F57">
-        <v>29.975</v>
+        <v>30.52</v>
       </c>
       <c r="G57">
         <v>4.39</v>
@@ -5961,37 +5961,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M57">
-        <v>7.068105000000001</v>
+        <v>7.196616000000001</v>
       </c>
       <c r="N57">
-        <v>-5.052798877551021</v>
+        <v>-5.181309877551022</v>
       </c>
       <c r="O57">
-        <v>-0.9095037979591838</v>
+        <v>-0.9326357779591838</v>
       </c>
       <c r="P57">
-        <v>-4.143295079591837</v>
+        <v>-4.248674099591838</v>
       </c>
       <c r="Q57">
-        <v>-0.8932950795918373</v>
+        <v>-0.9986740995918382</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1343102694492278</v>
+        <v>0.1363218664821648</v>
       </c>
       <c r="T57">
-        <v>1.49241029867968</v>
+        <v>1.526328714558764</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.05132282302552329</v>
+        <v>0.05040634404292465</v>
       </c>
       <c r="W57">
-        <v>0.2236980783305816</v>
+        <v>0.2239141840746784</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2851267945862405</v>
+        <v>0.2800352446829147</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1853735643339724</v>
+        <v>0.1872735643339724</v>
       </c>
       <c r="C58">
-        <v>-4.223606903244402</v>
+        <v>-5.006975753159203</v>
       </c>
       <c r="D58">
-        <v>21.9063930967556</v>
+        <v>21.6680242468408</v>
       </c>
       <c r="E58">
-        <v>11.52</v>
+        <v>12.065</v>
       </c>
       <c r="F58">
-        <v>30.52</v>
+        <v>31.065</v>
       </c>
       <c r="G58">
         <v>4.39</v>
@@ -6043,37 +6043,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M58">
-        <v>7.196616000000001</v>
+        <v>7.325127000000001</v>
       </c>
       <c r="N58">
-        <v>-5.181309877551022</v>
+        <v>-5.309820877551021</v>
       </c>
       <c r="O58">
-        <v>-0.9326357779591838</v>
+        <v>-0.9557677579591838</v>
       </c>
       <c r="P58">
-        <v>-4.248674099591838</v>
+        <v>-4.354053119591837</v>
       </c>
       <c r="Q58">
-        <v>-0.9986740995918382</v>
+        <v>-1.104053119591837</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1363218664821648</v>
+        <v>0.1384270261677965</v>
       </c>
       <c r="T58">
-        <v>1.526328714558764</v>
+        <v>1.56182473117641</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.05040634404292465</v>
+        <v>0.04952202221761019</v>
       </c>
       <c r="W58">
-        <v>0.2239141840746784</v>
+        <v>0.2241227071610875</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2800352446829147</v>
+        <v>0.27512234565339</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1872735643339724</v>
+        <v>0.1891735643339724</v>
       </c>
       <c r="C59">
-        <v>-5.006975753159203</v>
+        <v>-5.78521294180381</v>
       </c>
       <c r="D59">
-        <v>21.6680242468408</v>
+        <v>21.43478705819619</v>
       </c>
       <c r="E59">
-        <v>12.065</v>
+        <v>12.61</v>
       </c>
       <c r="F59">
-        <v>31.065</v>
+        <v>31.61</v>
       </c>
       <c r="G59">
         <v>4.39</v>
@@ -6125,37 +6125,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M59">
-        <v>7.325127000000001</v>
+        <v>7.453638000000001</v>
       </c>
       <c r="N59">
-        <v>-5.309820877551021</v>
+        <v>-5.438331877551021</v>
       </c>
       <c r="O59">
-        <v>-0.9557677579591838</v>
+        <v>-0.9788997379591837</v>
       </c>
       <c r="P59">
-        <v>-4.354053119591837</v>
+        <v>-4.459432139591837</v>
       </c>
       <c r="Q59">
-        <v>-1.104053119591837</v>
+        <v>-1.209432139591837</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1384270261677965</v>
+        <v>0.1406324315527441</v>
       </c>
       <c r="T59">
-        <v>1.56182473117641</v>
+        <v>1.599011034299657</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.04952202221761019</v>
+        <v>0.04866819424834105</v>
       </c>
       <c r="W59">
-        <v>0.2241227071610875</v>
+        <v>0.2243240397962412</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.27512234565339</v>
+        <v>0.2703788569352281</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1891735643339724</v>
+        <v>0.1910735643339724</v>
       </c>
       <c r="C60">
-        <v>-5.785212941803799</v>
+        <v>-6.558482417850929</v>
       </c>
       <c r="D60">
-        <v>21.4347870581962</v>
+        <v>21.20651758214907</v>
       </c>
       <c r="E60">
-        <v>12.61</v>
+        <v>13.155</v>
       </c>
       <c r="F60">
-        <v>31.61</v>
+        <v>32.155</v>
       </c>
       <c r="G60">
         <v>4.39</v>
@@ -6207,37 +6207,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M60">
-        <v>7.453638</v>
+        <v>7.582149</v>
       </c>
       <c r="N60">
-        <v>-5.43833187755102</v>
+        <v>-5.566842877551021</v>
       </c>
       <c r="O60">
-        <v>-0.9788997379591836</v>
+        <v>-1.002031717959184</v>
       </c>
       <c r="P60">
-        <v>-4.459432139591836</v>
+        <v>-4.564811159591837</v>
       </c>
       <c r="Q60">
-        <v>-1.209432139591836</v>
+        <v>-1.314811159591837</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.140632431552744</v>
+        <v>0.1429454176881768</v>
       </c>
       <c r="T60">
-        <v>1.599011034299657</v>
+        <v>1.638011303428917</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04866819424834106</v>
+        <v>0.04784330960006408</v>
       </c>
       <c r="W60">
-        <v>0.2243240397962412</v>
+        <v>0.2245185475963049</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2703788569352281</v>
+        <v>0.2657961644448005</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1910735643339724</v>
+        <v>0.1929735643339724</v>
       </c>
       <c r="C61">
-        <v>-6.558482417850929</v>
+        <v>-7.326941219687562</v>
       </c>
       <c r="D61">
-        <v>21.20651758214907</v>
+        <v>20.98305878031243</v>
       </c>
       <c r="E61">
-        <v>13.155</v>
+        <v>13.7</v>
       </c>
       <c r="F61">
-        <v>32.155</v>
+        <v>32.7</v>
       </c>
       <c r="G61">
         <v>4.39</v>
@@ -6289,37 +6289,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M61">
-        <v>7.582149</v>
+        <v>7.710659999999999</v>
       </c>
       <c r="N61">
-        <v>-5.566842877551021</v>
+        <v>-5.695353877551019</v>
       </c>
       <c r="O61">
-        <v>-1.002031717959184</v>
+        <v>-1.025163697959183</v>
       </c>
       <c r="P61">
-        <v>-4.564811159591837</v>
+        <v>-4.670190179591836</v>
       </c>
       <c r="Q61">
-        <v>-1.314811159591837</v>
+        <v>-1.420190179591836</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1429454176881768</v>
+        <v>0.1453740531303812</v>
       </c>
       <c r="T61">
-        <v>1.638011303428917</v>
+        <v>1.67896158601464</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04784330960006408</v>
+        <v>0.0470459211067297</v>
       </c>
       <c r="W61">
-        <v>0.2245185475963049</v>
+        <v>0.2247065718030332</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2657961644448005</v>
+        <v>0.2613662283707205</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1929735643339724</v>
+        <v>0.1948735643339724</v>
       </c>
       <c r="C62">
-        <v>-7.326941219687562</v>
+        <v>-8.090739835696318</v>
       </c>
       <c r="D62">
-        <v>20.98305878031243</v>
+        <v>20.76426016430368</v>
       </c>
       <c r="E62">
-        <v>13.7</v>
+        <v>14.245</v>
       </c>
       <c r="F62">
-        <v>32.7</v>
+        <v>33.245</v>
       </c>
       <c r="G62">
         <v>4.39</v>
@@ -6371,37 +6371,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M62">
-        <v>7.710659999999999</v>
+        <v>7.839170999999999</v>
       </c>
       <c r="N62">
-        <v>-5.695353877551019</v>
+        <v>-5.82386487755102</v>
       </c>
       <c r="O62">
-        <v>-1.025163697959183</v>
+        <v>-1.048295677959183</v>
       </c>
       <c r="P62">
-        <v>-4.670190179591836</v>
+        <v>-4.775569199591836</v>
       </c>
       <c r="Q62">
-        <v>-1.420190179591836</v>
+        <v>-1.525569199591836</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1453740531303812</v>
+        <v>0.1479272339798782</v>
       </c>
       <c r="T62">
-        <v>1.67896158601464</v>
+        <v>1.722011883091938</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.0470459211067297</v>
+        <v>0.04627467649842264</v>
       </c>
       <c r="W62">
-        <v>0.2247065718030332</v>
+        <v>0.2248884312816719</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2613662283707205</v>
+        <v>0.2570815361023481</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1948735643339724</v>
+        <v>0.1967735643339724</v>
       </c>
       <c r="C63">
-        <v>-8.090739835696318</v>
+        <v>-8.850022542228611</v>
       </c>
       <c r="D63">
-        <v>20.76426016430368</v>
+        <v>20.54997745777139</v>
       </c>
       <c r="E63">
-        <v>14.245</v>
+        <v>14.79</v>
       </c>
       <c r="F63">
-        <v>33.245</v>
+        <v>33.79</v>
       </c>
       <c r="G63">
         <v>4.39</v>
@@ -6453,37 +6453,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M63">
-        <v>7.839170999999999</v>
+        <v>7.967682</v>
       </c>
       <c r="N63">
-        <v>-5.82386487755102</v>
+        <v>-5.95237587755102</v>
       </c>
       <c r="O63">
-        <v>-1.048295677959183</v>
+        <v>-1.071427657959184</v>
       </c>
       <c r="P63">
-        <v>-4.775569199591836</v>
+        <v>-4.880948219591836</v>
       </c>
       <c r="Q63">
-        <v>-1.525569199591836</v>
+        <v>-1.630948219591836</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1479272339798782</v>
+        <v>0.1506147927688224</v>
       </c>
       <c r="T63">
-        <v>1.722011883091938</v>
+        <v>1.767327985278568</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04627467649842264</v>
+        <v>0.04552831074844808</v>
       </c>
       <c r="W63">
-        <v>0.2248884312816719</v>
+        <v>0.225064424325516</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2570815361023481</v>
+        <v>0.2529350597136005</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1967735643339724</v>
+        <v>0.1986735643339724</v>
       </c>
       <c r="C64">
-        <v>-8.850022542228611</v>
+        <v>-9.604927720864758</v>
       </c>
       <c r="D64">
-        <v>20.54997745777139</v>
+        <v>20.34007227913524</v>
       </c>
       <c r="E64">
-        <v>14.79</v>
+        <v>15.335</v>
       </c>
       <c r="F64">
-        <v>33.79</v>
+        <v>34.335</v>
       </c>
       <c r="G64">
         <v>4.39</v>
@@ -6535,37 +6535,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M64">
-        <v>7.967682</v>
+        <v>8.096193000000001</v>
       </c>
       <c r="N64">
-        <v>-5.95237587755102</v>
+        <v>-6.080886877551022</v>
       </c>
       <c r="O64">
-        <v>-1.071427657959184</v>
+        <v>-1.094559637959184</v>
       </c>
       <c r="P64">
-        <v>-4.880948219591836</v>
+        <v>-4.986327239591838</v>
       </c>
       <c r="Q64">
-        <v>-1.630948219591836</v>
+        <v>-1.736327239591838</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1506147927688224</v>
+        <v>0.1534476250058176</v>
       </c>
       <c r="T64">
-        <v>1.767327985278568</v>
+        <v>1.815093606502313</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04552831074844808</v>
+        <v>0.04480563914926636</v>
       </c>
       <c r="W64">
-        <v>0.225064424325516</v>
+        <v>0.225234830288603</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2529350597136005</v>
+        <v>0.2489202174959242</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1986735643339724</v>
+        <v>0.2005735643339724</v>
       </c>
       <c r="C65">
-        <v>-9.604927720864758</v>
+        <v>-10.35558815642697</v>
       </c>
       <c r="D65">
-        <v>20.34007227913524</v>
+        <v>20.13441184357303</v>
       </c>
       <c r="E65">
-        <v>15.335</v>
+        <v>15.88</v>
       </c>
       <c r="F65">
-        <v>34.335</v>
+        <v>34.88</v>
       </c>
       <c r="G65">
         <v>4.39</v>
@@ -6617,37 +6617,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M65">
-        <v>8.096193000000001</v>
+        <v>8.224704000000001</v>
       </c>
       <c r="N65">
-        <v>-6.080886877551022</v>
+        <v>-6.209397877551021</v>
       </c>
       <c r="O65">
-        <v>-1.094559637959184</v>
+        <v>-1.117691617959184</v>
       </c>
       <c r="P65">
-        <v>-4.986327239591838</v>
+        <v>-5.091706259591837</v>
       </c>
       <c r="Q65">
-        <v>-1.736327239591838</v>
+        <v>-1.841706259591837</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1534476250058176</v>
+        <v>0.1564378368115347</v>
       </c>
       <c r="T65">
-        <v>1.815093606502313</v>
+        <v>1.8655128733496</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04480563914926636</v>
+        <v>0.04410555103755908</v>
       </c>
       <c r="W65">
-        <v>0.225234830288603</v>
+        <v>0.2253999110653436</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2489202174959242</v>
+        <v>0.2450308390975504</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2005735643339724</v>
+        <v>0.2024735643339724</v>
       </c>
       <c r="C66">
-        <v>-10.35558815642697</v>
+        <v>-11.10213131709391</v>
       </c>
       <c r="D66">
-        <v>20.13441184357303</v>
+        <v>19.9328686829061</v>
       </c>
       <c r="E66">
-        <v>15.88</v>
+        <v>16.425</v>
       </c>
       <c r="F66">
-        <v>34.88</v>
+        <v>35.425</v>
       </c>
       <c r="G66">
         <v>4.39</v>
@@ -6699,37 +6699,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M66">
-        <v>8.224704000000001</v>
+        <v>8.353215000000001</v>
       </c>
       <c r="N66">
-        <v>-6.209397877551021</v>
+        <v>-6.337908877551021</v>
       </c>
       <c r="O66">
-        <v>-1.117691617959184</v>
+        <v>-1.140823597959184</v>
       </c>
       <c r="P66">
-        <v>-5.091706259591837</v>
+        <v>-5.197085279591837</v>
       </c>
       <c r="Q66">
-        <v>-1.841706259591837</v>
+        <v>-1.947085279591837</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1564378368115347</v>
+        <v>0.1595989178632929</v>
       </c>
       <c r="T66">
-        <v>1.8655128733496</v>
+        <v>1.918813241159589</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04410555103755908</v>
+        <v>0.04342700409851971</v>
       </c>
       <c r="W66">
-        <v>0.2253999110653436</v>
+        <v>0.225559912433569</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2450308390975504</v>
+        <v>0.2412611338806651</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2024735643339724</v>
+        <v>0.2043735643339724</v>
       </c>
       <c r="C67">
-        <v>-11.10213131709391</v>
+        <v>-11.84467961785845</v>
       </c>
       <c r="D67">
-        <v>19.9328686829061</v>
+        <v>19.73532038214155</v>
       </c>
       <c r="E67">
-        <v>16.425</v>
+        <v>16.97</v>
       </c>
       <c r="F67">
-        <v>35.425</v>
+        <v>35.97</v>
       </c>
       <c r="G67">
         <v>4.39</v>
@@ -6781,37 +6781,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M67">
-        <v>8.353215000000001</v>
+        <v>8.481726</v>
       </c>
       <c r="N67">
-        <v>-6.337908877551021</v>
+        <v>-6.46641987755102</v>
       </c>
       <c r="O67">
-        <v>-1.140823597959184</v>
+        <v>-1.163955577959184</v>
       </c>
       <c r="P67">
-        <v>-5.197085279591837</v>
+        <v>-5.302464299591836</v>
       </c>
       <c r="Q67">
-        <v>-1.947085279591837</v>
+        <v>-2.052464299591836</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1595989178632929</v>
+        <v>0.1629459448592721</v>
       </c>
       <c r="T67">
-        <v>1.918813241159589</v>
+        <v>1.975248924723106</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04342700409851971</v>
+        <v>0.04276901918793607</v>
       </c>
       <c r="W67">
-        <v>0.225559912433569</v>
+        <v>0.2257150652754847</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2412611338806651</v>
+        <v>0.2376056621552004</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2043735643339724</v>
+        <v>0.2062735643339724</v>
       </c>
       <c r="C68">
-        <v>-11.84467961785845</v>
+        <v>-12.58335066847297</v>
       </c>
       <c r="D68">
-        <v>19.73532038214155</v>
+        <v>19.54164933152703</v>
       </c>
       <c r="E68">
-        <v>16.97</v>
+        <v>17.515</v>
       </c>
       <c r="F68">
-        <v>35.97</v>
+        <v>36.515</v>
       </c>
       <c r="G68">
         <v>4.39</v>
@@ -6863,37 +6863,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M68">
-        <v>8.481726</v>
+        <v>8.610237</v>
       </c>
       <c r="N68">
-        <v>-6.46641987755102</v>
+        <v>-6.59493087755102</v>
       </c>
       <c r="O68">
-        <v>-1.163955577959184</v>
+        <v>-1.187087557959184</v>
       </c>
       <c r="P68">
-        <v>-5.302464299591836</v>
+        <v>-5.407843319591836</v>
       </c>
       <c r="Q68">
-        <v>-2.052464299591836</v>
+        <v>-2.157843319591836</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1629459448592721</v>
+        <v>0.1664958219762197</v>
       </c>
       <c r="T68">
-        <v>1.975248924723106</v>
+        <v>2.035104952745018</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04276901918793607</v>
+        <v>0.04213067561796689</v>
       </c>
       <c r="W68">
-        <v>0.2257150652754847</v>
+        <v>0.2258655866892834</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2376056621552004</v>
+        <v>0.234059308988705</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2062735643339724</v>
+        <v>0.2081735643339724</v>
       </c>
       <c r="C69">
-        <v>-12.58335066847297</v>
+        <v>-13.31825750693731</v>
       </c>
       <c r="D69">
-        <v>19.54164933152703</v>
+        <v>19.35174249306269</v>
       </c>
       <c r="E69">
-        <v>17.515</v>
+        <v>18.06</v>
       </c>
       <c r="F69">
-        <v>36.515</v>
+        <v>37.06</v>
       </c>
       <c r="G69">
         <v>4.39</v>
@@ -6945,37 +6945,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M69">
-        <v>8.610237</v>
+        <v>8.738748000000001</v>
       </c>
       <c r="N69">
-        <v>-6.59493087755102</v>
+        <v>-6.723441877551021</v>
       </c>
       <c r="O69">
-        <v>-1.187087557959184</v>
+        <v>-1.210219537959184</v>
       </c>
       <c r="P69">
-        <v>-5.407843319591836</v>
+        <v>-5.513222339591838</v>
       </c>
       <c r="Q69">
-        <v>-2.157843319591836</v>
+        <v>-2.263222339591838</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1664958219762197</v>
+        <v>0.1702675664129766</v>
       </c>
       <c r="T69">
-        <v>2.035104952745018</v>
+        <v>2.0987019825183</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04213067561796689</v>
+        <v>0.04151110685887913</v>
       </c>
       <c r="W69">
-        <v>0.2258655866892834</v>
+        <v>0.2260116810026763</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.234059308988705</v>
+        <v>0.2306172603271063</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2081735643339724</v>
+        <v>0.2100735643339724</v>
       </c>
       <c r="C70">
-        <v>-13.31825750693731</v>
+        <v>-14.04950881950344</v>
       </c>
       <c r="D70">
-        <v>19.35174249306269</v>
+        <v>19.16549118049656</v>
       </c>
       <c r="E70">
-        <v>18.06</v>
+        <v>18.605</v>
       </c>
       <c r="F70">
-        <v>37.06</v>
+        <v>37.605</v>
       </c>
       <c r="G70">
         <v>4.39</v>
@@ -7027,37 +7027,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M70">
-        <v>8.738748000000001</v>
+        <v>8.867259000000001</v>
       </c>
       <c r="N70">
-        <v>-6.723441877551021</v>
+        <v>-6.851952877551021</v>
       </c>
       <c r="O70">
-        <v>-1.210219537959184</v>
+        <v>-1.233351517959184</v>
       </c>
       <c r="P70">
-        <v>-5.513222339591838</v>
+        <v>-5.618601359591837</v>
       </c>
       <c r="Q70">
-        <v>-2.263222339591838</v>
+        <v>-2.368601359591837</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1702675664129766</v>
+        <v>0.174282649200492</v>
       </c>
       <c r="T70">
-        <v>2.0987019825183</v>
+        <v>2.166402046470504</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04151110685887913</v>
+        <v>0.04090949661454755</v>
       </c>
       <c r="W70">
-        <v>0.2260116810026763</v>
+        <v>0.2261535406982897</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2306172603271063</v>
+        <v>0.2272749811919308</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2100735643339724</v>
+        <v>0.2119735643339724</v>
       </c>
       <c r="C71">
-        <v>-14.04950881950344</v>
+        <v>-14.77720914809675</v>
       </c>
       <c r="D71">
-        <v>19.16549118049656</v>
+        <v>18.98279085190325</v>
       </c>
       <c r="E71">
-        <v>18.605</v>
+        <v>19.15000000000001</v>
       </c>
       <c r="F71">
-        <v>37.605</v>
+        <v>38.15000000000001</v>
       </c>
       <c r="G71">
         <v>4.39</v>
@@ -7109,37 +7109,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M71">
-        <v>8.867259000000001</v>
+        <v>8.995770000000002</v>
       </c>
       <c r="N71">
-        <v>-6.851952877551021</v>
+        <v>-6.980463877551022</v>
       </c>
       <c r="O71">
-        <v>-1.233351517959184</v>
+        <v>-1.256483497959184</v>
       </c>
       <c r="P71">
-        <v>-5.618601359591837</v>
+        <v>-5.723980379591838</v>
       </c>
       <c r="Q71">
-        <v>-2.368601359591837</v>
+        <v>-2.473980379591838</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.174282649200492</v>
+        <v>0.1785654041738417</v>
       </c>
       <c r="T71">
-        <v>2.166402046470504</v>
+        <v>2.23861544801952</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04090949661454755</v>
+        <v>0.04032507523433972</v>
       </c>
       <c r="W71">
-        <v>0.2261535406982897</v>
+        <v>0.2262913472597427</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2272749811919308</v>
+        <v>0.2240281957463318</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2119735643339724</v>
+        <v>0.2138735643339724</v>
       </c>
       <c r="C72">
-        <v>-14.77720914809675</v>
+        <v>-15.50145908598533</v>
       </c>
       <c r="D72">
-        <v>18.98279085190325</v>
+        <v>18.80354091401468</v>
       </c>
       <c r="E72">
-        <v>19.15000000000001</v>
+        <v>19.69500000000001</v>
       </c>
       <c r="F72">
-        <v>38.15000000000001</v>
+        <v>38.69500000000001</v>
       </c>
       <c r="G72">
         <v>4.39</v>
@@ -7191,37 +7191,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M72">
-        <v>8.995770000000002</v>
+        <v>9.124281000000002</v>
       </c>
       <c r="N72">
-        <v>-6.980463877551022</v>
+        <v>-7.108974877551022</v>
       </c>
       <c r="O72">
-        <v>-1.256483497959184</v>
+        <v>-1.279615477959184</v>
       </c>
       <c r="P72">
-        <v>-5.723980379591838</v>
+        <v>-5.829359399591838</v>
       </c>
       <c r="Q72">
-        <v>-2.473980379591838</v>
+        <v>-2.579359399591838</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1785654041738417</v>
+        <v>0.1831435215591466</v>
       </c>
       <c r="T72">
-        <v>2.23861544801952</v>
+        <v>2.315809084158125</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04032507523433972</v>
+        <v>0.03975711642822226</v>
       </c>
       <c r="W72">
-        <v>0.2262913472597427</v>
+        <v>0.2264252719462252</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2240281957463318</v>
+        <v>0.2208728690456793</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2138735643339724</v>
+        <v>0.2157735643339724</v>
       </c>
       <c r="C73">
-        <v>-15.50145908598532</v>
+        <v>-16.2223554624672</v>
       </c>
       <c r="D73">
-        <v>18.80354091401468</v>
+        <v>18.6276445375328</v>
       </c>
       <c r="E73">
-        <v>19.695</v>
+        <v>20.24</v>
       </c>
       <c r="F73">
-        <v>38.695</v>
+        <v>39.24</v>
       </c>
       <c r="G73">
         <v>4.39</v>
@@ -7273,37 +7273,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M73">
-        <v>9.124281</v>
+        <v>9.252792000000001</v>
       </c>
       <c r="N73">
-        <v>-7.10897487755102</v>
+        <v>-7.237485877551022</v>
       </c>
       <c r="O73">
-        <v>-1.279615477959184</v>
+        <v>-1.302747457959184</v>
       </c>
       <c r="P73">
-        <v>-5.829359399591837</v>
+        <v>-5.934738419591838</v>
       </c>
       <c r="Q73">
-        <v>-2.579359399591837</v>
+        <v>-2.684738419591838</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1831435215591466</v>
+        <v>0.1880486473291161</v>
       </c>
       <c r="T73">
-        <v>2.315809084158124</v>
+        <v>2.398516551449485</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03975711642822227</v>
+        <v>0.03920493425560807</v>
       </c>
       <c r="W73">
-        <v>0.2264252719462252</v>
+        <v>0.2265554765025276</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2208728690456793</v>
+        <v>0.2178051903089337</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2157735643339724</v>
+        <v>0.2176735643339724</v>
       </c>
       <c r="C74">
-        <v>-16.2223554624672</v>
+        <v>-16.9399915172877</v>
       </c>
       <c r="D74">
-        <v>18.6276445375328</v>
+        <v>18.45500848271229</v>
       </c>
       <c r="E74">
-        <v>20.24</v>
+        <v>20.785</v>
       </c>
       <c r="F74">
-        <v>39.24</v>
+        <v>39.785</v>
       </c>
       <c r="G74">
         <v>4.39</v>
@@ -7355,37 +7355,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M74">
-        <v>9.252792000000001</v>
+        <v>9.381302999999999</v>
       </c>
       <c r="N74">
-        <v>-7.237485877551022</v>
+        <v>-7.365996877551019</v>
       </c>
       <c r="O74">
-        <v>-1.302747457959184</v>
+        <v>-1.325879437959183</v>
       </c>
       <c r="P74">
-        <v>-5.934738419591838</v>
+        <v>-6.040117439591836</v>
       </c>
       <c r="Q74">
-        <v>-2.684738419591838</v>
+        <v>-2.790117439591836</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1880486473291161</v>
+        <v>0.193317115748713</v>
       </c>
       <c r="T74">
-        <v>2.398516551449485</v>
+        <v>2.487350497799466</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03920493425560807</v>
+        <v>0.03866788036169563</v>
       </c>
       <c r="W74">
-        <v>0.2265554765025276</v>
+        <v>0.2266821138107122</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2178051903089337</v>
+        <v>0.2148215575649758</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2176735643339724</v>
+        <v>0.2195735643339724</v>
       </c>
       <c r="C75">
-        <v>-16.9399915172877</v>
+        <v>-17.65445706544715</v>
       </c>
       <c r="D75">
-        <v>18.45500848271229</v>
+        <v>18.28554293455285</v>
       </c>
       <c r="E75">
-        <v>20.785</v>
+        <v>21.33</v>
       </c>
       <c r="F75">
-        <v>39.785</v>
+        <v>40.33</v>
       </c>
       <c r="G75">
         <v>4.39</v>
@@ -7437,37 +7437,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M75">
-        <v>9.381302999999999</v>
+        <v>9.509814</v>
       </c>
       <c r="N75">
-        <v>-7.365996877551019</v>
+        <v>-7.494507877551021</v>
       </c>
       <c r="O75">
-        <v>-1.325879437959183</v>
+        <v>-1.349011417959184</v>
       </c>
       <c r="P75">
-        <v>-6.040117439591836</v>
+        <v>-6.145496459591837</v>
       </c>
       <c r="Q75">
-        <v>-2.790117439591836</v>
+        <v>-2.895496459591837</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.193317115748713</v>
+        <v>0.1989908509698173</v>
       </c>
       <c r="T75">
-        <v>2.487350497799466</v>
+        <v>2.583017824637907</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03866788036169563</v>
+        <v>0.03814534143788893</v>
       </c>
       <c r="W75">
-        <v>0.2266821138107122</v>
+        <v>0.2268053284889458</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2148215575649758</v>
+        <v>0.2119185635438274</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2195735643339724</v>
+        <v>0.2214735643339724</v>
       </c>
       <c r="C76">
-        <v>-17.65445706544715</v>
+        <v>-18.36583865301094</v>
       </c>
       <c r="D76">
-        <v>18.28554293455285</v>
+        <v>18.11916134698906</v>
       </c>
       <c r="E76">
-        <v>21.33</v>
+        <v>21.875</v>
       </c>
       <c r="F76">
-        <v>40.33</v>
+        <v>40.875</v>
       </c>
       <c r="G76">
         <v>4.39</v>
@@ -7519,37 +7519,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M76">
-        <v>9.509814</v>
+        <v>9.638325</v>
       </c>
       <c r="N76">
-        <v>-7.494507877551021</v>
+        <v>-7.62301887755102</v>
       </c>
       <c r="O76">
-        <v>-1.349011417959184</v>
+        <v>-1.372143397959184</v>
       </c>
       <c r="P76">
-        <v>-6.145496459591837</v>
+        <v>-6.250875479591837</v>
       </c>
       <c r="Q76">
-        <v>-2.895496459591837</v>
+        <v>-3.000875479591837</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1989908509698173</v>
+        <v>0.20511848500861</v>
       </c>
       <c r="T76">
-        <v>2.583017824637907</v>
+        <v>2.686338537623424</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03814534143788893</v>
+        <v>0.03763673688538375</v>
       </c>
       <c r="W76">
-        <v>0.2268053284889458</v>
+        <v>0.2269252574424265</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2119185635438274</v>
+        <v>0.2090929826965764</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2214735643339724</v>
+        <v>0.2233735643339724</v>
       </c>
       <c r="C77">
-        <v>-18.36583865301094</v>
+        <v>-19.07421970449004</v>
       </c>
       <c r="D77">
-        <v>18.11916134698906</v>
+        <v>17.95578029550996</v>
       </c>
       <c r="E77">
-        <v>21.875</v>
+        <v>22.42</v>
       </c>
       <c r="F77">
-        <v>40.875</v>
+        <v>41.42</v>
       </c>
       <c r="G77">
         <v>4.39</v>
@@ -7601,37 +7601,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M77">
-        <v>9.638325</v>
+        <v>9.766836000000001</v>
       </c>
       <c r="N77">
-        <v>-7.62301887755102</v>
+        <v>-7.751529877551022</v>
       </c>
       <c r="O77">
-        <v>-1.372143397959184</v>
+        <v>-1.395275377959184</v>
       </c>
       <c r="P77">
-        <v>-6.250875479591837</v>
+        <v>-6.356254499591838</v>
       </c>
       <c r="Q77">
-        <v>-3.000875479591837</v>
+        <v>-3.106254499591838</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.20511848500861</v>
+        <v>0.2117567552173021</v>
       </c>
       <c r="T77">
-        <v>2.686338537623424</v>
+        <v>2.7982693100244</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03763673688538375</v>
+        <v>0.03714151666320764</v>
       </c>
       <c r="W77">
-        <v>0.2269252574424265</v>
+        <v>0.2270420303708156</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2090929826965764</v>
+        <v>0.2063417592400425</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2233735643339724</v>
+        <v>0.2252735643339724</v>
       </c>
       <c r="C78">
-        <v>-19.07421970449004</v>
+        <v>-19.77968066231908</v>
       </c>
       <c r="D78">
-        <v>17.95578029550996</v>
+        <v>17.79531933768093</v>
       </c>
       <c r="E78">
-        <v>22.42</v>
+        <v>22.965</v>
       </c>
       <c r="F78">
-        <v>41.42</v>
+        <v>41.965</v>
       </c>
       <c r="G78">
         <v>4.39</v>
@@ -7683,37 +7683,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M78">
-        <v>9.766836000000001</v>
+        <v>9.895347000000001</v>
       </c>
       <c r="N78">
-        <v>-7.751529877551022</v>
+        <v>-7.880040877551021</v>
       </c>
       <c r="O78">
-        <v>-1.395275377959184</v>
+        <v>-1.418407357959184</v>
       </c>
       <c r="P78">
-        <v>-6.356254499591838</v>
+        <v>-6.461633519591837</v>
       </c>
       <c r="Q78">
-        <v>-3.106254499591838</v>
+        <v>-3.211633519591837</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2117567552173021</v>
+        <v>0.2189722663137065</v>
       </c>
       <c r="T78">
-        <v>2.7982693100244</v>
+        <v>2.919933193068939</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03714151666320764</v>
+        <v>0.03665915930394521</v>
       </c>
       <c r="W78">
-        <v>0.2270420303708156</v>
+        <v>0.2271557702361297</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2063417592400425</v>
+        <v>0.2036619961330289</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2252735643339724</v>
+        <v>0.2271735643339724</v>
       </c>
       <c r="C79">
-        <v>-19.77968066231908</v>
+        <v>-20.48229911892202</v>
       </c>
       <c r="D79">
-        <v>17.79531933768093</v>
+        <v>17.63770088107798</v>
       </c>
       <c r="E79">
-        <v>22.965</v>
+        <v>23.51</v>
       </c>
       <c r="F79">
-        <v>41.965</v>
+        <v>42.51</v>
       </c>
       <c r="G79">
         <v>4.39</v>
@@ -7765,37 +7765,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M79">
-        <v>9.895347000000001</v>
+        <v>10.023858</v>
       </c>
       <c r="N79">
-        <v>-7.880040877551021</v>
+        <v>-8.008551877551021</v>
       </c>
       <c r="O79">
-        <v>-1.418407357959184</v>
+        <v>-1.441539337959184</v>
       </c>
       <c r="P79">
-        <v>-6.461633519591837</v>
+        <v>-6.567012539591837</v>
       </c>
       <c r="Q79">
-        <v>-3.211633519591837</v>
+        <v>-3.317012539591837</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2189722663137065</v>
+        <v>0.2268437329643296</v>
       </c>
       <c r="T79">
-        <v>2.919933193068939</v>
+        <v>3.052657429117527</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03665915930394521</v>
+        <v>0.03618917008209976</v>
       </c>
       <c r="W79">
-        <v>0.2271557702361297</v>
+        <v>0.2272665936946409</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2036619961330289</v>
+        <v>0.2010509449005542</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2271735643339724</v>
+        <v>0.2290735643339724</v>
       </c>
       <c r="C80">
-        <v>-20.48229911892202</v>
+        <v>-21.18214994182105</v>
       </c>
       <c r="D80">
-        <v>17.63770088107798</v>
+        <v>17.48285005817895</v>
       </c>
       <c r="E80">
-        <v>23.51</v>
+        <v>24.055</v>
       </c>
       <c r="F80">
-        <v>42.51</v>
+        <v>43.055</v>
       </c>
       <c r="G80">
         <v>4.39</v>
@@ -7847,37 +7847,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M80">
-        <v>10.023858</v>
+        <v>10.152369</v>
       </c>
       <c r="N80">
-        <v>-8.008551877551021</v>
+        <v>-8.137062877551021</v>
       </c>
       <c r="O80">
-        <v>-1.441539337959184</v>
+        <v>-1.464671317959184</v>
       </c>
       <c r="P80">
-        <v>-6.567012539591837</v>
+        <v>-6.672391559591837</v>
       </c>
       <c r="Q80">
-        <v>-3.317012539591837</v>
+        <v>-3.422391559591837</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2268437329643296</v>
+        <v>0.2354648631054881</v>
       </c>
       <c r="T80">
-        <v>3.052657429117527</v>
+        <v>3.198022068599315</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03618917008209976</v>
+        <v>0.03573107932156685</v>
       </c>
       <c r="W80">
-        <v>0.2272665936946409</v>
+        <v>0.2273746114959745</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2010509449005542</v>
+        <v>0.1985059962309269</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2290735643339724</v>
+        <v>0.2309735643339724</v>
       </c>
       <c r="C81">
-        <v>-21.18214994182105</v>
+        <v>-21.87930539221236</v>
       </c>
       <c r="D81">
-        <v>17.48285005817895</v>
+        <v>17.33069460778764</v>
       </c>
       <c r="E81">
-        <v>24.055</v>
+        <v>24.6</v>
       </c>
       <c r="F81">
-        <v>43.055</v>
+        <v>43.6</v>
       </c>
       <c r="G81">
         <v>4.39</v>
@@ -7929,37 +7929,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M81">
-        <v>10.152369</v>
+        <v>10.28088</v>
       </c>
       <c r="N81">
-        <v>-8.137062877551021</v>
+        <v>-8.265573877551022</v>
       </c>
       <c r="O81">
-        <v>-1.464671317959184</v>
+        <v>-1.487803297959184</v>
       </c>
       <c r="P81">
-        <v>-6.672391559591837</v>
+        <v>-6.777770579591838</v>
       </c>
       <c r="Q81">
-        <v>-3.422391559591837</v>
+        <v>-3.527770579591838</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2354648631054881</v>
+        <v>0.2449481062607626</v>
       </c>
       <c r="T81">
-        <v>3.198022068599315</v>
+        <v>3.357923172029281</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03573107932156685</v>
+        <v>0.03528444083004726</v>
       </c>
       <c r="W81">
-        <v>0.2273746114959745</v>
+        <v>0.2274799288522749</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1985059962309269</v>
+        <v>0.1960246712780404</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2309735643339724</v>
+        <v>0.2328735643339724</v>
       </c>
       <c r="C82">
-        <v>-21.87930539221236</v>
+        <v>-22.57383523740354</v>
       </c>
       <c r="D82">
-        <v>17.33069460778764</v>
+        <v>17.18116476259646</v>
       </c>
       <c r="E82">
-        <v>24.6</v>
+        <v>25.145</v>
       </c>
       <c r="F82">
-        <v>43.6</v>
+        <v>44.145</v>
       </c>
       <c r="G82">
         <v>4.39</v>
@@ -8011,37 +8011,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M82">
-        <v>10.28088</v>
+        <v>10.409391</v>
       </c>
       <c r="N82">
-        <v>-8.265573877551022</v>
+        <v>-8.394084877551022</v>
       </c>
       <c r="O82">
-        <v>-1.487803297959184</v>
+        <v>-1.510935277959184</v>
       </c>
       <c r="P82">
-        <v>-6.777770579591838</v>
+        <v>-6.883149599591838</v>
       </c>
       <c r="Q82">
-        <v>-3.527770579591838</v>
+        <v>-3.633149599591838</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2449481062607626</v>
+        <v>0.2554295855376448</v>
       </c>
       <c r="T82">
-        <v>3.357923172029281</v>
+        <v>3.534655970557138</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03528444083004726</v>
+        <v>0.03484883044942939</v>
       </c>
       <c r="W82">
-        <v>0.2274799288522749</v>
+        <v>0.2275826457800245</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1960246712780404</v>
+        <v>0.1936046136079411</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2328735643339724</v>
+        <v>0.2347735643339724</v>
       </c>
       <c r="C83">
-        <v>-22.57383523740354</v>
+        <v>-23.26580685748005</v>
       </c>
       <c r="D83">
-        <v>17.18116476259646</v>
+        <v>17.03419314251995</v>
       </c>
       <c r="E83">
-        <v>25.145</v>
+        <v>25.69</v>
       </c>
       <c r="F83">
-        <v>44.145</v>
+        <v>44.69</v>
       </c>
       <c r="G83">
         <v>4.39</v>
@@ -8093,37 +8093,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M83">
-        <v>10.409391</v>
+        <v>10.537902</v>
       </c>
       <c r="N83">
-        <v>-8.394084877551022</v>
+        <v>-8.522595877551021</v>
       </c>
       <c r="O83">
-        <v>-1.510935277959184</v>
+        <v>-1.534067257959184</v>
       </c>
       <c r="P83">
-        <v>-6.883149599591838</v>
+        <v>-6.988528619591838</v>
       </c>
       <c r="Q83">
-        <v>-3.633149599591838</v>
+        <v>-3.738528619591838</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2554295855376448</v>
+        <v>0.2670756736230696</v>
       </c>
       <c r="T83">
-        <v>3.534655970557138</v>
+        <v>3.731025746699201</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03484883044942939</v>
+        <v>0.03442384471224123</v>
       </c>
       <c r="W83">
-        <v>0.2275826457800245</v>
+        <v>0.2276828574168535</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1936046136079411</v>
+        <v>0.1912435817346735</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2347735643339724</v>
+        <v>0.2366735643339724</v>
       </c>
       <c r="C84">
-        <v>-23.26580685748005</v>
+        <v>-23.95528534654341</v>
       </c>
       <c r="D84">
-        <v>17.03419314251995</v>
+        <v>16.88971465345659</v>
       </c>
       <c r="E84">
-        <v>25.69</v>
+        <v>26.23500000000001</v>
       </c>
       <c r="F84">
-        <v>44.69</v>
+        <v>45.23500000000001</v>
       </c>
       <c r="G84">
         <v>4.39</v>
@@ -8175,37 +8175,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M84">
-        <v>10.537902</v>
+        <v>10.666413</v>
       </c>
       <c r="N84">
-        <v>-8.522595877551021</v>
+        <v>-8.651106877551022</v>
       </c>
       <c r="O84">
-        <v>-1.534067257959184</v>
+        <v>-1.557199237959184</v>
       </c>
       <c r="P84">
-        <v>-6.988528619591838</v>
+        <v>-7.093907639591839</v>
       </c>
       <c r="Q84">
-        <v>-3.738528619591838</v>
+        <v>-3.843907639591839</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2670756736230696</v>
+        <v>0.2800918897185442</v>
       </c>
       <c r="T84">
-        <v>3.731025746699201</v>
+        <v>3.950497849446213</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03442384471224123</v>
+        <v>0.03400909959522627</v>
       </c>
       <c r="W84">
-        <v>0.2276828574168535</v>
+        <v>0.2277806543154457</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1912435817346735</v>
+        <v>0.1889394421957015</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2366735643339724</v>
+        <v>0.2385735643339724</v>
       </c>
       <c r="C85">
-        <v>-23.95528534654341</v>
+        <v>-24.64233360884072</v>
       </c>
       <c r="D85">
-        <v>16.88971465345659</v>
+        <v>16.74766639115928</v>
       </c>
       <c r="E85">
-        <v>26.23500000000001</v>
+        <v>26.78</v>
       </c>
       <c r="F85">
-        <v>45.23500000000001</v>
+        <v>45.78</v>
       </c>
       <c r="G85">
         <v>4.39</v>
@@ -8257,37 +8257,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M85">
-        <v>10.666413</v>
+        <v>10.794924</v>
       </c>
       <c r="N85">
-        <v>-8.651106877551022</v>
+        <v>-8.77961787755102</v>
       </c>
       <c r="O85">
-        <v>-1.557199237959184</v>
+        <v>-1.580331217959184</v>
       </c>
       <c r="P85">
-        <v>-7.093907639591839</v>
+        <v>-7.199286659591837</v>
       </c>
       <c r="Q85">
-        <v>-3.843907639591839</v>
+        <v>-3.949286659591837</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2800918897185442</v>
+        <v>0.2947351328259533</v>
       </c>
       <c r="T85">
-        <v>3.950497849446213</v>
+        <v>4.197403965036602</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03400909959522627</v>
+        <v>0.03360422936194978</v>
       </c>
       <c r="W85">
-        <v>0.2277806543154457</v>
+        <v>0.2278761227164523</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1889394421957015</v>
+        <v>0.1866901631219432</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2385735643339724</v>
+        <v>0.2404735643339724</v>
       </c>
       <c r="C86">
-        <v>-24.64233360884072</v>
+        <v>-25.32701245008379</v>
       </c>
       <c r="D86">
-        <v>16.74766639115929</v>
+        <v>16.60798754991621</v>
       </c>
       <c r="E86">
-        <v>26.78</v>
+        <v>27.325</v>
       </c>
       <c r="F86">
-        <v>45.78</v>
+        <v>46.325</v>
       </c>
       <c r="G86">
         <v>4.39</v>
@@ -8339,37 +8339,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M86">
-        <v>10.794924</v>
+        <v>10.923435</v>
       </c>
       <c r="N86">
-        <v>-8.77961787755102</v>
+        <v>-8.90812887755102</v>
       </c>
       <c r="O86">
-        <v>-1.580331217959184</v>
+        <v>-1.603463197959184</v>
       </c>
       <c r="P86">
-        <v>-7.199286659591837</v>
+        <v>-7.304665679591836</v>
       </c>
       <c r="Q86">
-        <v>-3.949286659591837</v>
+        <v>-4.054665679591836</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2947351328259531</v>
+        <v>0.3113308083476833</v>
       </c>
       <c r="T86">
-        <v>4.1974039650366</v>
+        <v>4.477230896039039</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03360422936194978</v>
+        <v>0.03320888548710331</v>
       </c>
       <c r="W86">
-        <v>0.2278761227164523</v>
+        <v>0.227969344802141</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1866901631219432</v>
+        <v>0.184493808261685</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2404735643339724</v>
+        <v>0.2423735643339724</v>
       </c>
       <c r="C87">
-        <v>-25.32701245008379</v>
+        <v>-26.00938066423628</v>
       </c>
       <c r="D87">
-        <v>16.60798754991621</v>
+        <v>16.47061933576371</v>
       </c>
       <c r="E87">
-        <v>27.325</v>
+        <v>27.87</v>
       </c>
       <c r="F87">
-        <v>46.325</v>
+        <v>46.87</v>
       </c>
       <c r="G87">
         <v>4.39</v>
@@ -8421,37 +8421,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M87">
-        <v>10.923435</v>
+        <v>11.051946</v>
       </c>
       <c r="N87">
-        <v>-8.90812887755102</v>
+        <v>-9.036639877551019</v>
       </c>
       <c r="O87">
-        <v>-1.603463197959184</v>
+        <v>-1.626595177959183</v>
       </c>
       <c r="P87">
-        <v>-7.304665679591836</v>
+        <v>-7.410044699591836</v>
       </c>
       <c r="Q87">
-        <v>-4.054665679591836</v>
+        <v>-4.160044699591836</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3113308083476833</v>
+        <v>0.3302972946582322</v>
       </c>
       <c r="T87">
-        <v>4.477230896039039</v>
+        <v>4.797033102898971</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03320888548710331</v>
+        <v>0.03282273565585792</v>
       </c>
       <c r="W87">
-        <v>0.227969344802141</v>
+        <v>0.2280603989323487</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.184493808261685</v>
+        <v>0.1823485314214329</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2423735643339724</v>
+        <v>0.2442735643339724</v>
       </c>
       <c r="C88">
-        <v>-26.00938066423628</v>
+        <v>-26.68949511602919</v>
       </c>
       <c r="D88">
-        <v>16.47061933576371</v>
+        <v>16.33550488397081</v>
       </c>
       <c r="E88">
-        <v>27.87</v>
+        <v>28.415</v>
       </c>
       <c r="F88">
-        <v>46.87</v>
+        <v>47.415</v>
       </c>
       <c r="G88">
         <v>4.39</v>
@@ -8503,37 +8503,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M88">
-        <v>11.051946</v>
+        <v>11.180457</v>
       </c>
       <c r="N88">
-        <v>-9.036639877551019</v>
+        <v>-9.165150877551021</v>
       </c>
       <c r="O88">
-        <v>-1.626595177959183</v>
+        <v>-1.649727157959184</v>
       </c>
       <c r="P88">
-        <v>-7.410044699591836</v>
+        <v>-7.515423719591837</v>
       </c>
       <c r="Q88">
-        <v>-4.160044699591836</v>
+        <v>-4.265423719591837</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3302972946582322</v>
+        <v>0.3521817019396346</v>
       </c>
       <c r="T88">
-        <v>4.797033102898971</v>
+        <v>5.166035649275814</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03282273565585792</v>
+        <v>0.03244546283222736</v>
       </c>
       <c r="W88">
-        <v>0.2280603989323487</v>
+        <v>0.2281493598641608</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1823485314214329</v>
+        <v>0.180252571290152</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2442735643339724</v>
+        <v>0.2461735643339724</v>
       </c>
       <c r="C89">
-        <v>-26.68949511602919</v>
+        <v>-27.36741081944798</v>
       </c>
       <c r="D89">
-        <v>16.33550488397081</v>
+        <v>16.20258918055202</v>
       </c>
       <c r="E89">
-        <v>28.415</v>
+        <v>28.96</v>
       </c>
       <c r="F89">
-        <v>47.415</v>
+        <v>47.96</v>
       </c>
       <c r="G89">
         <v>4.39</v>
@@ -8585,37 +8585,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M89">
-        <v>11.180457</v>
+        <v>11.308968</v>
       </c>
       <c r="N89">
-        <v>-9.165150877551021</v>
+        <v>-9.29366187755102</v>
       </c>
       <c r="O89">
-        <v>-1.649727157959184</v>
+        <v>-1.672859137959184</v>
       </c>
       <c r="P89">
-        <v>-7.515423719591837</v>
+        <v>-7.620802739591837</v>
       </c>
       <c r="Q89">
-        <v>-4.265423719591837</v>
+        <v>-4.370802739591837</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3521817019396346</v>
+        <v>0.3777135104346042</v>
       </c>
       <c r="T89">
-        <v>5.166035649275814</v>
+        <v>5.5965386200488</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03244546283222736</v>
+        <v>0.03207676439095206</v>
       </c>
       <c r="W89">
-        <v>0.2281493598641608</v>
+        <v>0.2282362989566135</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.180252571290152</v>
+        <v>0.1782042466164003</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2461735643339724</v>
+        <v>0.2480735643339724</v>
       </c>
       <c r="C90">
-        <v>-27.36741081944798</v>
+        <v>-28.04318101241886</v>
       </c>
       <c r="D90">
-        <v>16.20258918055202</v>
+        <v>16.07181898758114</v>
       </c>
       <c r="E90">
-        <v>28.96</v>
+        <v>29.505</v>
       </c>
       <c r="F90">
-        <v>47.96</v>
+        <v>48.505</v>
       </c>
       <c r="G90">
         <v>4.39</v>
@@ -8667,37 +8667,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M90">
-        <v>11.308968</v>
+        <v>11.437479</v>
       </c>
       <c r="N90">
-        <v>-9.29366187755102</v>
+        <v>-9.422172877551022</v>
       </c>
       <c r="O90">
-        <v>-1.672859137959184</v>
+        <v>-1.695991117959184</v>
       </c>
       <c r="P90">
-        <v>-7.620802739591837</v>
+        <v>-7.726181759591838</v>
       </c>
       <c r="Q90">
-        <v>-4.370802739591837</v>
+        <v>-4.476181759591838</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3777135104346042</v>
+        <v>0.4078874659286592</v>
       </c>
       <c r="T90">
-        <v>5.5965386200488</v>
+        <v>6.105314858235054</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03207676439095206</v>
+        <v>0.03171635130790765</v>
       </c>
       <c r="W90">
-        <v>0.2282362989566135</v>
+        <v>0.2283212843615954</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1782042466164003</v>
+        <v>0.176201951710598</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2480735643339724</v>
+        <v>0.2499735643339724</v>
       </c>
       <c r="C91">
-        <v>-28.04318101241886</v>
+        <v>-28.7168572279074</v>
       </c>
       <c r="D91">
-        <v>16.07181898758114</v>
+        <v>15.9431427720926</v>
       </c>
       <c r="E91">
-        <v>29.505</v>
+        <v>30.05</v>
       </c>
       <c r="F91">
-        <v>48.505</v>
+        <v>49.05</v>
       </c>
       <c r="G91">
         <v>4.39</v>
@@ -8749,37 +8749,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M91">
-        <v>11.437479</v>
+        <v>11.56599</v>
       </c>
       <c r="N91">
-        <v>-9.422172877551022</v>
+        <v>-9.550683877551021</v>
       </c>
       <c r="O91">
-        <v>-1.695991117959184</v>
+        <v>-1.719123097959184</v>
       </c>
       <c r="P91">
-        <v>-7.726181759591838</v>
+        <v>-7.831560779591838</v>
       </c>
       <c r="Q91">
-        <v>-4.476181759591838</v>
+        <v>-4.581560779591838</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4078874659286592</v>
+        <v>0.4440962125215251</v>
       </c>
       <c r="T91">
-        <v>6.105314858235054</v>
+        <v>6.715846344058561</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03171635130790765</v>
+        <v>0.03136394740448645</v>
       </c>
       <c r="W91">
-        <v>0.2283212843615954</v>
+        <v>0.2284043812020221</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.176201951710598</v>
+        <v>0.174244152247147</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2499735643339724</v>
+        <v>0.2518735643339724</v>
       </c>
       <c r="C92">
-        <v>-28.7168572279074</v>
+        <v>-29.38848936162868</v>
       </c>
       <c r="D92">
-        <v>15.9431427720926</v>
+        <v>15.81651063837132</v>
       </c>
       <c r="E92">
-        <v>30.05</v>
+        <v>30.595</v>
       </c>
       <c r="F92">
-        <v>49.05</v>
+        <v>49.595</v>
       </c>
       <c r="G92">
         <v>4.39</v>
@@ -8831,37 +8831,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M92">
-        <v>11.56599</v>
+        <v>11.694501</v>
       </c>
       <c r="N92">
-        <v>-9.550683877551021</v>
+        <v>-9.679194877551021</v>
       </c>
       <c r="O92">
-        <v>-1.719123097959184</v>
+        <v>-1.742255077959184</v>
       </c>
       <c r="P92">
-        <v>-7.831560779591838</v>
+        <v>-7.936939799591837</v>
       </c>
       <c r="Q92">
-        <v>-4.581560779591838</v>
+        <v>-4.686939799591837</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4440962125215251</v>
+        <v>0.4883513472461391</v>
       </c>
       <c r="T92">
-        <v>6.715846344058561</v>
+        <v>7.462051493398402</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03136394740448645</v>
+        <v>0.03101928864179979</v>
       </c>
       <c r="W92">
-        <v>0.2284043812020221</v>
+        <v>0.2284856517382636</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.174244152247147</v>
+        <v>0.1723293813433322</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2518735643339724</v>
+        <v>0.2537735643339724</v>
       </c>
       <c r="C93">
-        <v>-29.38848936162868</v>
+        <v>-30.05812573655624</v>
       </c>
       <c r="D93">
-        <v>15.81651063837132</v>
+        <v>15.69187426344376</v>
       </c>
       <c r="E93">
-        <v>30.595</v>
+        <v>31.14</v>
       </c>
       <c r="F93">
-        <v>49.595</v>
+        <v>50.14</v>
       </c>
       <c r="G93">
         <v>4.39</v>
@@ -8913,37 +8913,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M93">
-        <v>11.694501</v>
+        <v>11.823012</v>
       </c>
       <c r="N93">
-        <v>-9.679194877551021</v>
+        <v>-9.807705877551021</v>
       </c>
       <c r="O93">
-        <v>-1.742255077959184</v>
+        <v>-1.765387057959184</v>
       </c>
       <c r="P93">
-        <v>-7.936939799591837</v>
+        <v>-8.042318819591838</v>
       </c>
       <c r="Q93">
-        <v>-4.686939799591837</v>
+        <v>-4.792318819591838</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4883513472461391</v>
+        <v>0.5436702656519066</v>
       </c>
       <c r="T93">
-        <v>7.462051493398402</v>
+        <v>8.394807930073204</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03101928864179979</v>
+        <v>0.03068212246091067</v>
       </c>
       <c r="W93">
-        <v>0.2284856517382636</v>
+        <v>0.2285651555237173</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1723293813433322</v>
+        <v>0.1704562358939481</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2537735643339724</v>
+        <v>0.2556735643339724</v>
       </c>
       <c r="C94">
-        <v>-30.05812573655624</v>
+        <v>-30.72581316440463</v>
       </c>
       <c r="D94">
-        <v>15.69187426344376</v>
+        <v>15.56918683559537</v>
       </c>
       <c r="E94">
-        <v>31.14</v>
+        <v>31.685</v>
       </c>
       <c r="F94">
-        <v>50.14</v>
+        <v>50.685</v>
       </c>
       <c r="G94">
         <v>4.39</v>
@@ -8995,37 +8995,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M94">
-        <v>11.823012</v>
+        <v>11.951523</v>
       </c>
       <c r="N94">
-        <v>-9.807705877551021</v>
+        <v>-9.936216877551022</v>
       </c>
       <c r="O94">
-        <v>-1.765387057959184</v>
+        <v>-1.788519037959184</v>
       </c>
       <c r="P94">
-        <v>-8.042318819591838</v>
+        <v>-8.147697839591839</v>
       </c>
       <c r="Q94">
-        <v>-4.792318819591838</v>
+        <v>-4.897697839591839</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5436702656519066</v>
+        <v>0.6147945893164647</v>
       </c>
       <c r="T94">
-        <v>8.394807930073204</v>
+        <v>9.594066205797949</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03068212246091067</v>
+        <v>0.03035220716563206</v>
       </c>
       <c r="W94">
-        <v>0.2285651555237173</v>
+        <v>0.228642949550344</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1704562358939481</v>
+        <v>0.1686233731424003</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2556735643339724</v>
+        <v>0.2575735643339724</v>
       </c>
       <c r="C95">
-        <v>-30.72581316440463</v>
+        <v>-31.39159700425028</v>
       </c>
       <c r="D95">
-        <v>15.56918683559537</v>
+        <v>15.44840299574973</v>
       </c>
       <c r="E95">
-        <v>31.685</v>
+        <v>32.23</v>
       </c>
       <c r="F95">
-        <v>50.685</v>
+        <v>51.23</v>
       </c>
       <c r="G95">
         <v>4.39</v>
@@ -9077,37 +9077,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M95">
-        <v>11.951523</v>
+        <v>12.080034</v>
       </c>
       <c r="N95">
-        <v>-9.936216877551022</v>
+        <v>-10.06472787755102</v>
       </c>
       <c r="O95">
-        <v>-1.788519037959184</v>
+        <v>-1.811651017959184</v>
       </c>
       <c r="P95">
-        <v>-8.147697839591839</v>
+        <v>-8.253076859591838</v>
       </c>
       <c r="Q95">
-        <v>-4.897697839591839</v>
+        <v>-5.003076859591838</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6147945893164647</v>
+        <v>0.7096270208692089</v>
       </c>
       <c r="T95">
-        <v>9.594066205797949</v>
+        <v>11.19307724009761</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03035220716563206</v>
+        <v>0.03002931134472107</v>
       </c>
       <c r="W95">
-        <v>0.228642949550344</v>
+        <v>0.2287190883849148</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1686233731424003</v>
+        <v>0.1668295074706726</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2575735643339724</v>
+        <v>0.2594735643339725</v>
       </c>
       <c r="C96">
-        <v>-31.39159700425028</v>
+        <v>-32.05552121844467</v>
       </c>
       <c r="D96">
-        <v>15.44840299574973</v>
+        <v>15.32947878155534</v>
       </c>
       <c r="E96">
-        <v>32.23</v>
+        <v>32.77500000000001</v>
       </c>
       <c r="F96">
-        <v>51.23</v>
+        <v>51.77500000000001</v>
       </c>
       <c r="G96">
         <v>4.39</v>
@@ -9159,37 +9159,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M96">
-        <v>12.080034</v>
+        <v>12.208545</v>
       </c>
       <c r="N96">
-        <v>-10.06472787755102</v>
+        <v>-10.19323887755102</v>
       </c>
       <c r="O96">
-        <v>-1.811651017959184</v>
+        <v>-1.834782997959184</v>
       </c>
       <c r="P96">
-        <v>-8.253076859591838</v>
+        <v>-8.358455879591839</v>
       </c>
       <c r="Q96">
-        <v>-5.003076859591838</v>
+        <v>-5.108455879591839</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7096270208692089</v>
+        <v>0.8423924250430511</v>
       </c>
       <c r="T96">
-        <v>11.19307724009761</v>
+        <v>13.43169268811714</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03002931134472107</v>
+        <v>0.02971321333056611</v>
       </c>
       <c r="W96">
-        <v>0.2287190883849148</v>
+        <v>0.2287936242966525</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1668295074706726</v>
+        <v>0.1650734073920339</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2594735643339725</v>
+        <v>0.2613735643339724</v>
       </c>
       <c r="C97">
-        <v>-32.05552121844467</v>
+        <v>-32.71762842596461</v>
       </c>
       <c r="D97">
-        <v>15.32947878155534</v>
+        <v>15.21237157403539</v>
       </c>
       <c r="E97">
-        <v>32.77500000000001</v>
+        <v>33.32000000000001</v>
       </c>
       <c r="F97">
-        <v>51.77500000000001</v>
+        <v>52.32000000000001</v>
       </c>
       <c r="G97">
         <v>4.39</v>
@@ -9241,37 +9241,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M97">
-        <v>12.208545</v>
+        <v>12.337056</v>
       </c>
       <c r="N97">
-        <v>-10.19323887755102</v>
+        <v>-10.32174987755102</v>
       </c>
       <c r="O97">
-        <v>-1.834782997959184</v>
+        <v>-1.857914977959184</v>
       </c>
       <c r="P97">
-        <v>-8.358455879591839</v>
+        <v>-8.463834899591838</v>
       </c>
       <c r="Q97">
-        <v>-5.108455879591839</v>
+        <v>-5.213834899591838</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8423924250430511</v>
+        <v>1.041540531303814</v>
       </c>
       <c r="T97">
-        <v>13.43169268811714</v>
+        <v>16.78961586014643</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02971321333056611</v>
+        <v>0.02940370069170605</v>
       </c>
       <c r="W97">
-        <v>0.2287936242966525</v>
+        <v>0.2288666073768957</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1650734073920339</v>
+        <v>0.1633538927317003</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2613735643339724</v>
+        <v>0.2632735643339724</v>
       </c>
       <c r="C98">
-        <v>-32.71762842596461</v>
+        <v>-33.37795995333585</v>
       </c>
       <c r="D98">
-        <v>15.21237157403539</v>
+        <v>15.09704004666416</v>
       </c>
       <c r="E98">
-        <v>33.32</v>
+        <v>33.865</v>
       </c>
       <c r="F98">
-        <v>52.32</v>
+        <v>52.865</v>
       </c>
       <c r="G98">
         <v>4.39</v>
@@ -9323,37 +9323,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M98">
-        <v>12.337056</v>
+        <v>12.465567</v>
       </c>
       <c r="N98">
-        <v>-10.32174987755102</v>
+        <v>-10.45026087755102</v>
       </c>
       <c r="O98">
-        <v>-1.857914977959184</v>
+        <v>-1.881046957959184</v>
       </c>
       <c r="P98">
-        <v>-8.463834899591838</v>
+        <v>-8.569213919591839</v>
       </c>
       <c r="Q98">
-        <v>-5.213834899591838</v>
+        <v>-5.319213919591839</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.041540531303812</v>
+        <v>1.373454041738416</v>
       </c>
       <c r="T98">
-        <v>16.78961586014638</v>
+        <v>22.38615448019518</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02940370069170605</v>
+        <v>0.02910056975674001</v>
       </c>
       <c r="W98">
-        <v>0.2288666073768957</v>
+        <v>0.2289380856513607</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1633538927317003</v>
+        <v>0.1616698319818889</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2632735643339724</v>
+        <v>0.2651735643339724</v>
       </c>
       <c r="C99">
-        <v>-33.37795995333585</v>
+        <v>-34.03655588325744</v>
       </c>
       <c r="D99">
-        <v>15.09704004666416</v>
+        <v>14.98344411674256</v>
       </c>
       <c r="E99">
-        <v>33.865</v>
+        <v>34.41</v>
       </c>
       <c r="F99">
-        <v>52.865</v>
+        <v>53.41</v>
       </c>
       <c r="G99">
         <v>4.39</v>
@@ -9405,37 +9405,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M99">
-        <v>12.465567</v>
+        <v>12.594078</v>
       </c>
       <c r="N99">
-        <v>-10.45026087755102</v>
+        <v>-10.57877187755102</v>
       </c>
       <c r="O99">
-        <v>-1.881046957959184</v>
+        <v>-1.904178937959184</v>
       </c>
       <c r="P99">
-        <v>-8.569213919591839</v>
+        <v>-8.674592939591836</v>
       </c>
       <c r="Q99">
-        <v>-5.319213919591839</v>
+        <v>-5.424592939591836</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.373454041738416</v>
+        <v>2.037281062607623</v>
       </c>
       <c r="T99">
-        <v>22.38615448019518</v>
+        <v>33.57923172029277</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02910056975674001</v>
+        <v>0.02880362516738552</v>
       </c>
       <c r="W99">
-        <v>0.2289380856513607</v>
+        <v>0.2290081051855305</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1616698319818889</v>
+        <v>0.1600201398188085</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2651735643339724</v>
+        <v>0.2670735643339724</v>
       </c>
       <c r="C100">
-        <v>-34.03655588325744</v>
+        <v>-34.69345510104752</v>
       </c>
       <c r="D100">
-        <v>14.98344411674256</v>
+        <v>14.87154489895248</v>
       </c>
       <c r="E100">
-        <v>34.41</v>
+        <v>34.955</v>
       </c>
       <c r="F100">
-        <v>53.41</v>
+        <v>53.955</v>
       </c>
       <c r="G100">
         <v>4.39</v>
@@ -9487,37 +9487,37 @@
         <v>2.01530612244898</v>
       </c>
       <c r="M100">
-        <v>12.594078</v>
+        <v>12.722589</v>
       </c>
       <c r="N100">
-        <v>-10.57877187755102</v>
+        <v>-10.70728287755102</v>
       </c>
       <c r="O100">
-        <v>-1.904178937959184</v>
+        <v>-1.927310917959183</v>
       </c>
       <c r="P100">
-        <v>-8.674592939591836</v>
+        <v>-8.779971959591837</v>
       </c>
       <c r="Q100">
-        <v>-5.424592939591836</v>
+        <v>-5.529971959591837</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.037281062607623</v>
+        <v>4.028762125215247</v>
       </c>
       <c r="T100">
-        <v>33.57923172029277</v>
+        <v>67.15846344058554</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02880362516738552</v>
+        <v>0.02851267945862405</v>
       </c>
       <c r="W100">
-        <v>0.2290081051855305</v>
+        <v>0.2290767101836565</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1600201398188085</v>
+        <v>0.1584037747701337</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2670735643339724</v>
-      </c>
-      <c r="C101">
-        <v>-34.69345510104752</v>
-      </c>
-      <c r="D101">
-        <v>14.87154489895248</v>
-      </c>
-      <c r="E101">
-        <v>34.955</v>
-      </c>
-      <c r="F101">
-        <v>53.955</v>
-      </c>
-      <c r="G101">
-        <v>4.39</v>
-      </c>
-      <c r="H101">
-        <v>35.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.26530612244898</v>
-      </c>
-      <c r="K101">
-        <v>3.25</v>
-      </c>
-      <c r="L101">
-        <v>2.01530612244898</v>
-      </c>
-      <c r="M101">
-        <v>12.722589</v>
-      </c>
-      <c r="N101">
-        <v>-10.70728287755102</v>
-      </c>
-      <c r="O101">
-        <v>-1.927310917959183</v>
-      </c>
-      <c r="P101">
-        <v>-8.779971959591837</v>
-      </c>
-      <c r="Q101">
-        <v>-5.529971959591837</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.028762125215247</v>
-      </c>
-      <c r="T101">
-        <v>67.15846344058554</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02851267945862405</v>
-      </c>
-      <c r="W101">
-        <v>0.2290767101836565</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1584037747701337</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
